--- a/source-excel/ADMIX.xlsx
+++ b/source-excel/ADMIX.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\ข้อมูลทำ AI\newstarrating\source-excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABCFBEB-BFF6-4EE7-AA55-DE23050324FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE359722-9CD9-4959-818A-44FE63C6833F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{92A2D19A-1020-4C8B-8BFE-BB6C01A75159}"/>
   </bookViews>
@@ -2403,7 +2403,7 @@
         <v>2.4875621890547261</v>
       </c>
       <c r="L2" s="11">
-        <v>0</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="M2" s="11">
         <v>0</v>
@@ -2415,10 +2415,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="11">
-        <v>1.2914877001171416</v>
+        <v>1.3079697698385435</v>
       </c>
       <c r="Q2" s="15">
-        <v>1.0791658713494943</v>
+        <v>1.120839983448602</v>
       </c>
       <c r="R2" s="12">
         <v>5</v>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="11">
-        <v>0</v>
+        <v>4.4642857142857144</v>
       </c>
       <c r="M3" s="11">
         <v>0</v>
@@ -2471,10 +2471,10 @@
         <v>0</v>
       </c>
       <c r="P3" s="11">
-        <v>1.0329953753112771</v>
+        <v>1.1000174398325777</v>
       </c>
       <c r="Q3" s="15">
-        <v>1.0791658713494943</v>
+        <v>1.120839983448602</v>
       </c>
       <c r="R3" s="12">
         <v>5</v>
@@ -2515,7 +2515,7 @@
         <v>1.0378827192527245</v>
       </c>
       <c r="L4" s="11">
-        <v>0</v>
+        <v>0.99734042553191493</v>
       </c>
       <c r="M4" s="11">
         <v>0</v>
@@ -2527,10 +2527,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="11">
-        <v>1.1274104327146772</v>
+        <v>1.1180265745670841</v>
       </c>
       <c r="Q4" s="15">
-        <v>1.0791658713494943</v>
+        <v>1.120839983448602</v>
       </c>
       <c r="R4" s="12">
         <v>5</v>
@@ -2571,7 +2571,7 @@
         <v>1.1160714285714286</v>
       </c>
       <c r="L5" s="11">
-        <v>0</v>
+        <v>3.4562211981566819</v>
       </c>
       <c r="M5" s="11">
         <v>0</v>
@@ -2583,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="11">
-        <v>0.76765609007164792</v>
+        <v>1.0363887609396591</v>
       </c>
       <c r="Q5" s="15">
-        <v>1.0791658713494943</v>
+        <v>1.120839983448602</v>
       </c>
       <c r="R5" s="12">
         <v>5</v>
@@ -2639,10 +2639,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="11">
-        <v>1.1066914917625819</v>
+        <v>1.0592396587104438</v>
       </c>
       <c r="Q6" s="15">
-        <v>1.1066914917625819</v>
+        <v>1.0592396587104438</v>
       </c>
       <c r="R6" s="12">
         <v>5</v>
@@ -2683,7 +2683,7 @@
         <v>0.98554533508541398</v>
       </c>
       <c r="L7" s="11">
-        <v>0</v>
+        <v>1.0438413361169103</v>
       </c>
       <c r="M7" s="11">
         <v>0</v>
@@ -2695,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="P7" s="11">
-        <v>0.91616602949208081</v>
+        <v>0.92992090564906094</v>
       </c>
       <c r="Q7" s="15">
-        <v>1.1318712020674722</v>
+        <v>1.1092321567662855</v>
       </c>
       <c r="R7" s="12">
         <v>5</v>
@@ -2739,7 +2739,7 @@
         <v>3.4246575342465753</v>
       </c>
       <c r="L8" s="11">
-        <v>0</v>
+        <v>1.0344827586206897</v>
       </c>
       <c r="M8" s="11">
         <v>0</v>
@@ -2751,10 +2751,10 @@
         <v>0</v>
       </c>
       <c r="P8" s="11">
-        <v>2.1070703917590135</v>
+        <v>1.9091256204658267</v>
       </c>
       <c r="Q8" s="15">
-        <v>1.1318712020674722</v>
+        <v>1.1092321567662855</v>
       </c>
       <c r="R8" s="12">
         <v>5</v>
@@ -2795,7 +2795,7 @@
         <v>1.3149243918474687</v>
       </c>
       <c r="L9" s="11">
-        <v>0</v>
+        <v>0.66181336863004636</v>
       </c>
       <c r="M9" s="11">
         <v>0</v>
@@ -2807,10 +2807,10 @@
         <v>0</v>
       </c>
       <c r="P9" s="11">
-        <v>1.0444627580252728</v>
+        <v>1.0038941902890823</v>
       </c>
       <c r="Q9" s="15">
-        <v>1.1318712020674722</v>
+        <v>1.1092321567662855</v>
       </c>
       <c r="R9" s="12">
         <v>5</v>
@@ -2851,7 +2851,7 @@
         <v>1.5060240963855422</v>
       </c>
       <c r="L10" s="11">
-        <v>0</v>
+        <v>1.0845986984815619</v>
       </c>
       <c r="M10" s="11">
         <v>0</v>
@@ -2863,10 +2863,10 @@
         <v>0</v>
       </c>
       <c r="P10" s="11">
-        <v>1.3843567685157718</v>
+        <v>1.3712880650652544</v>
       </c>
       <c r="Q10" s="15">
-        <v>1.3843567685157718</v>
+        <v>1.3712880650652544</v>
       </c>
       <c r="R10" s="12">
         <v>5</v>
@@ -2904,10 +2904,10 @@
         <v>0.57870370370370372</v>
       </c>
       <c r="K11" s="11">
-        <v>2.109704641350211</v>
+        <v>2.1276595744680851</v>
       </c>
       <c r="L11" s="11">
-        <v>0</v>
+        <v>1.0649627263045793</v>
       </c>
       <c r="M11" s="11">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P11" s="11">
-        <v>1.0856638787245165</v>
+        <v>1.0839059042739023</v>
       </c>
       <c r="Q11" s="15">
-        <v>1.0403935639401245</v>
+        <v>1.0615529819907148</v>
       </c>
       <c r="R11" s="12">
         <v>5</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="11">
-        <v>0.54288816503800219</v>
+        <v>0.5305039787798409</v>
       </c>
       <c r="Q12" s="15">
-        <v>1.0403935639401245</v>
+        <v>1.0615529819907148</v>
       </c>
       <c r="R12" s="12">
         <v>5</v>
@@ -3019,7 +3019,7 @@
         <v>3.5971223021582732</v>
       </c>
       <c r="L13" s="11">
-        <v>0</v>
+        <v>4.1946308724832218</v>
       </c>
       <c r="M13" s="11">
         <v>0</v>
@@ -3031,10 +3031,10 @@
         <v>0</v>
       </c>
       <c r="P13" s="11">
-        <v>2.0803827030284769</v>
+        <v>2.2545969860362227</v>
       </c>
       <c r="Q13" s="15">
-        <v>1.0403935639401245</v>
+        <v>1.0615529819907148</v>
       </c>
       <c r="R13" s="12">
         <v>5</v>
@@ -3075,7 +3075,7 @@
         <v>2.5906735751295336</v>
       </c>
       <c r="L14" s="11">
-        <v>0</v>
+        <v>0.93808630393996251</v>
       </c>
       <c r="M14" s="11">
         <v>0</v>
@@ -3087,10 +3087,10 @@
         <v>0</v>
       </c>
       <c r="P14" s="11">
-        <v>1.1605977078195271</v>
+        <v>1.1446269862644762</v>
       </c>
       <c r="Q14" s="15">
-        <v>1.0403935639401245</v>
+        <v>1.0615529819907148</v>
       </c>
       <c r="R14" s="12">
         <v>5</v>
@@ -3131,7 +3131,7 @@
         <v>2.2935779816513762</v>
       </c>
       <c r="L15" s="11">
-        <v>0</v>
+        <v>1.4705882352941178</v>
       </c>
       <c r="M15" s="11">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="P15" s="11">
-        <v>1.4008872285780996</v>
+        <v>1.4060134112048452</v>
       </c>
       <c r="Q15" s="15">
-        <v>1.0403935639401245</v>
+        <v>1.0615529819907148</v>
       </c>
       <c r="R15" s="12">
         <v>5</v>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="Q16" s="15">
-        <v>1.0403935639401245</v>
+        <v>1.0615529819907148</v>
       </c>
       <c r="R16" s="12">
         <v>5</v>
@@ -3243,7 +3243,7 @@
         <v>1.1947431302270013</v>
       </c>
       <c r="L17" s="11">
-        <v>0</v>
+        <v>2.4330900243309004</v>
       </c>
       <c r="M17" s="11">
         <v>0</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="P17" s="11">
-        <v>1.0222335803731153</v>
+        <v>1.0926308121889037</v>
       </c>
       <c r="Q17" s="15">
-        <v>1.0222335803731153</v>
+        <v>1.0926308121889037</v>
       </c>
       <c r="R17" s="12">
         <v>5</v>
@@ -3299,7 +3299,7 @@
         <v>0.59571088165210484</v>
       </c>
       <c r="L18" s="11">
-        <v>0</v>
+        <v>0.47755491881566381</v>
       </c>
       <c r="M18" s="11">
         <v>0</v>
@@ -3311,10 +3311,10 @@
         <v>0</v>
       </c>
       <c r="P18" s="11">
-        <v>0.48224086386149656</v>
+        <v>0.48203171625884561</v>
       </c>
       <c r="Q18" s="15">
-        <v>0.53936877824657292</v>
+        <v>0.54200169276343635</v>
       </c>
       <c r="R18" s="12">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0.70646414694454251</v>
       </c>
       <c r="L19" s="11">
-        <v>0</v>
+        <v>0.75795856493178371</v>
       </c>
       <c r="M19" s="11">
         <v>0</v>
@@ -3367,10 +3367,10 @@
         <v>0</v>
       </c>
       <c r="P19" s="11">
-        <v>0.58554971106830644</v>
+        <v>0.59732528041415012</v>
       </c>
       <c r="Q19" s="15">
-        <v>0.53936877824657292</v>
+        <v>0.54200169276343635</v>
       </c>
       <c r="R19" s="12">
         <v>0</v>
@@ -3411,7 +3411,7 @@
         <v>0.35945363048166784</v>
       </c>
       <c r="L20" s="11">
-        <v>0</v>
+        <v>0.48355899419729209</v>
       </c>
       <c r="M20" s="11">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>0</v>
       </c>
       <c r="P20" s="11">
-        <v>0.44328677200213723</v>
+        <v>0.44623275557127695</v>
       </c>
       <c r="Q20" s="15">
-        <v>0.53936877824657292</v>
+        <v>0.54200169276343635</v>
       </c>
       <c r="R20" s="12">
         <v>0</v>
@@ -3479,10 +3479,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="11">
-        <v>0.85511849499144876</v>
+        <v>0.80981027302174924</v>
       </c>
       <c r="Q21" s="15">
-        <v>0.53936877824657292</v>
+        <v>0.54200169276343635</v>
       </c>
       <c r="R21" s="12">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>1.3888888888888888</v>
       </c>
       <c r="L22" s="11">
-        <v>0</v>
+        <v>0.76452599388379205</v>
       </c>
       <c r="M22" s="11">
         <v>0</v>
@@ -3535,10 +3535,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="11">
-        <v>1.1348161597821154</v>
+        <v>1.1092330445806042</v>
       </c>
       <c r="Q22" s="15">
-        <v>1.2565124118908979</v>
+        <v>1.2224938875305624</v>
       </c>
       <c r="R22" s="12">
         <v>5</v>
@@ -3579,7 +3579,7 @@
         <v>1.2820512820512822</v>
       </c>
       <c r="L23" s="11">
-        <v>0</v>
+        <v>0.92081031307550643</v>
       </c>
       <c r="M23" s="11">
         <v>0</v>
@@ -3591,10 +3591,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="11">
-        <v>1.4460700918679823</v>
+        <v>1.4016508332035509</v>
       </c>
       <c r="Q23" s="15">
-        <v>1.2565124118908979</v>
+        <v>1.2224938875305624</v>
       </c>
       <c r="R23" s="12">
         <v>5</v>
@@ -3647,10 +3647,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="11">
-        <v>1.2307692307692308</v>
+        <v>1.1764705882352942</v>
       </c>
       <c r="Q24" s="15">
-        <v>1.2565124118908979</v>
+        <v>1.2224938875305624</v>
       </c>
       <c r="R24" s="12">
         <v>5</v>
@@ -3691,7 +3691,7 @@
         <v>1.098901098901099</v>
       </c>
       <c r="L25" s="11">
-        <v>0</v>
+        <v>0.92250922509225097</v>
       </c>
       <c r="M25" s="11">
         <v>0</v>
@@ -3703,10 +3703,10 @@
         <v>0</v>
       </c>
       <c r="P25" s="11">
-        <v>0.92478421701602964</v>
+        <v>0.924515988688275</v>
       </c>
       <c r="Q25" s="15">
-        <v>0.93854566228678693</v>
+        <v>0.96573431575935331</v>
       </c>
       <c r="R25" s="12">
         <v>5</v>
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="11">
-        <v>0</v>
+        <v>1.557632398753894</v>
       </c>
       <c r="M26" s="11">
         <v>0</v>
@@ -3759,10 +3759,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="11">
-        <v>0.96548394882935074</v>
+        <v>1.044932079414838</v>
       </c>
       <c r="Q26" s="15">
-        <v>0.93854566228678693</v>
+        <v>0.96573431575935331</v>
       </c>
       <c r="R26" s="12">
         <v>5</v>
@@ -3803,7 +3803,7 @@
         <v>1.6778523489932886</v>
       </c>
       <c r="L27" s="11">
-        <v>0</v>
+        <v>1.2515644555694618</v>
       </c>
       <c r="M27" s="11">
         <v>0</v>
@@ -3815,10 +3815,10 @@
         <v>0</v>
       </c>
       <c r="P27" s="11">
-        <v>1.3249819320645628</v>
+        <v>1.3131313131313131</v>
       </c>
       <c r="Q27" s="15">
-        <v>1.3249819320645628</v>
+        <v>1.3131313131313131</v>
       </c>
       <c r="R27" s="12">
         <v>5</v>
@@ -3859,7 +3859,7 @@
         <v>0.9502090459901178</v>
       </c>
       <c r="L28" s="11">
-        <v>0</v>
+        <v>1.1775788977861517</v>
       </c>
       <c r="M28" s="11">
         <v>0</v>
@@ -3871,10 +3871,10 @@
         <v>0</v>
       </c>
       <c r="P28" s="11">
-        <v>0.99428371441903873</v>
+        <v>1.0108054175688872</v>
       </c>
       <c r="Q28" s="15">
-        <v>1.0016195524146054</v>
+        <v>1.0049022172461781</v>
       </c>
       <c r="R28" s="12">
         <v>5</v>
@@ -3915,7 +3915,7 @@
         <v>0.99760574620909814</v>
       </c>
       <c r="L29" s="11">
-        <v>0</v>
+        <v>0.86565096952908582</v>
       </c>
       <c r="M29" s="11">
         <v>0</v>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="P29" s="11">
-        <v>1.0274616645771049</v>
+        <v>1.0076822145094388</v>
       </c>
       <c r="Q29" s="15">
-        <v>1.0016195524146054</v>
+        <v>1.0049022172461781</v>
       </c>
       <c r="R29" s="12">
         <v>5</v>
@@ -3971,7 +3971,7 @@
         <v>1.1286681715575622</v>
       </c>
       <c r="L30" s="11">
-        <v>0</v>
+        <v>1.3648771610555051</v>
       </c>
       <c r="M30" s="11">
         <v>0</v>
@@ -3983,10 +3983,10 @@
         <v>0</v>
       </c>
       <c r="P30" s="11">
-        <v>0.9949860958961827</v>
+        <v>1.0263381150701836</v>
       </c>
       <c r="Q30" s="15">
-        <v>1.0016195524146054</v>
+        <v>1.0049022172461781</v>
       </c>
       <c r="R30" s="12">
         <v>5</v>
@@ -4027,7 +4027,7 @@
         <v>0.93109869646182497</v>
       </c>
       <c r="L31" s="11">
-        <v>0</v>
+        <v>1.075268817204301</v>
       </c>
       <c r="M31" s="11">
         <v>0</v>
@@ -4039,10 +4039,10 @@
         <v>0</v>
       </c>
       <c r="P31" s="11">
-        <v>0.92593318695106652</v>
+        <v>0.93118710751305134</v>
       </c>
       <c r="Q31" s="15">
-        <v>1.0016195524146054</v>
+        <v>1.0049022172461781</v>
       </c>
       <c r="R31" s="12">
         <v>5</v>
@@ -4083,7 +4083,7 @@
         <v>0.91274187659729833</v>
       </c>
       <c r="L32" s="11">
-        <v>0</v>
+        <v>0.97703957010258913</v>
       </c>
       <c r="M32" s="11">
         <v>0</v>
@@ -4095,10 +4095,10 @@
         <v>0</v>
       </c>
       <c r="P32" s="11">
-        <v>1.0383426268425993</v>
+        <v>1.027041023100824</v>
       </c>
       <c r="Q32" s="15">
-        <v>1.0016195524146054</v>
+        <v>1.0049022172461781</v>
       </c>
       <c r="R32" s="12">
         <v>5</v>
@@ -4151,10 +4151,10 @@
         <v>0</v>
       </c>
       <c r="P33" s="11">
-        <v>0.96933380331335917</v>
+        <v>0.94017094017094016</v>
       </c>
       <c r="Q33" s="15">
-        <v>0.96933380331335917</v>
+        <v>0.94017094017094016</v>
       </c>
       <c r="R33" s="12">
         <v>5</v>
@@ -4207,10 +4207,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="11">
-        <v>1.165748198389148</v>
+        <v>1.0839574300354751</v>
       </c>
       <c r="Q34" s="15">
-        <v>1.165748198389148</v>
+        <v>1.0839574300354751</v>
       </c>
       <c r="R34" s="12">
         <v>5</v>
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="11">
-        <v>0</v>
+        <v>0.81833060556464809</v>
       </c>
       <c r="M35" s="11">
         <v>0</v>
@@ -4263,13 +4263,13 @@
         <v>0</v>
       </c>
       <c r="P35" s="11">
-        <v>1.0602341389728096</v>
+        <v>0.98385012919896642</v>
       </c>
       <c r="Q35" s="15">
-        <v>0.81400405914757901</v>
+        <v>0.79306394501145594</v>
       </c>
       <c r="R35" s="12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -4322,10 +4322,10 @@
         <v>0</v>
       </c>
       <c r="Q36" s="15">
-        <v>0.81400405914757901</v>
+        <v>0.79306394501145594</v>
       </c>
       <c r="R36" s="12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -4363,7 +4363,7 @@
         <v>0.76103500761035003</v>
       </c>
       <c r="L37" s="11">
-        <v>0</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="M37" s="11">
         <v>0</v>
@@ -4375,10 +4375,10 @@
         <v>0</v>
       </c>
       <c r="P37" s="11">
-        <v>0.8370579090555772</v>
+        <v>0.8195533583361746</v>
       </c>
       <c r="Q37" s="15">
-        <v>0.8370579090555772</v>
+        <v>0.8195533583361746</v>
       </c>
       <c r="R37" s="12">
         <v>4</v>
@@ -4419,7 +4419,7 @@
         <v>1.3812154696132597</v>
       </c>
       <c r="L38" s="11">
-        <v>0</v>
+        <v>1.1160714285714286</v>
       </c>
       <c r="M38" s="11">
         <v>0</v>
@@ -4431,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="P38" s="11">
-        <v>1.2036927271649576</v>
+        <v>1.1952794298880136</v>
       </c>
       <c r="Q38" s="15">
-        <v>1.0800838454028598</v>
+        <v>1.0725981091216394</v>
       </c>
       <c r="R38" s="12">
         <v>5</v>
@@ -4487,10 +4487,10 @@
         <v>0</v>
       </c>
       <c r="P39" s="11">
-        <v>1.0438413361169103</v>
+        <v>0.91116173120728927</v>
       </c>
       <c r="Q39" s="15">
-        <v>1.0800838454028598</v>
+        <v>1.0725981091216394</v>
       </c>
       <c r="R39" s="12">
         <v>5</v>
@@ -4531,7 +4531,7 @@
         <v>1.053370786516854</v>
       </c>
       <c r="L40" s="11">
-        <v>0</v>
+        <v>1.0319917440660475</v>
       </c>
       <c r="M40" s="11">
         <v>0</v>
@@ -4543,10 +4543,10 @@
         <v>0</v>
       </c>
       <c r="P40" s="11">
-        <v>0.95439241847995515</v>
+        <v>0.95881349952963313</v>
       </c>
       <c r="Q40" s="15">
-        <v>1.0800838454028598</v>
+        <v>1.0725981091216394</v>
       </c>
       <c r="R40" s="12">
         <v>5</v>
@@ -4587,7 +4587,7 @@
         <v>0.6839945280437757</v>
       </c>
       <c r="L41" s="11">
-        <v>0</v>
+        <v>1.6339869281045751</v>
       </c>
       <c r="M41" s="11">
         <v>0</v>
@@ -4599,10 +4599,10 @@
         <v>0</v>
       </c>
       <c r="P41" s="11">
-        <v>0.96107640557424312</v>
+        <v>1.0473397570171763</v>
       </c>
       <c r="Q41" s="15">
-        <v>0.99080144828261085</v>
+        <v>1.0325073274713563</v>
       </c>
       <c r="R41" s="12">
         <v>5</v>
@@ -4643,7 +4643,7 @@
         <v>1.5105740181268883</v>
       </c>
       <c r="L42" s="11">
-        <v>0</v>
+        <v>1.3623978201634876</v>
       </c>
       <c r="M42" s="11">
         <v>0</v>
@@ -4655,10 +4655,10 @@
         <v>0</v>
       </c>
       <c r="P42" s="11">
-        <v>0.99840255591054317</v>
+        <v>1.0285166816952209</v>
       </c>
       <c r="Q42" s="15">
-        <v>0.99080144828261085</v>
+        <v>1.0325073274713563</v>
       </c>
       <c r="R42" s="12">
         <v>5</v>
@@ -4699,7 +4699,7 @@
         <v>1.5923566878980893</v>
       </c>
       <c r="L43" s="11">
-        <v>0</v>
+        <v>0.52465897166841557</v>
       </c>
       <c r="M43" s="11">
         <v>0</v>
@@ -4711,10 +4711,10 @@
         <v>0</v>
       </c>
       <c r="P43" s="11">
-        <v>0.88131609870740302</v>
+        <v>0.83752093802345062</v>
       </c>
       <c r="Q43" s="15">
-        <v>0.88131609870740302</v>
+        <v>0.83752093802345062</v>
       </c>
       <c r="R43" s="12">
         <v>4</v>
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="11">
-        <v>0</v>
+        <v>2.0661157024793386</v>
       </c>
       <c r="M44" s="11">
         <v>0</v>
@@ -4767,10 +4767,10 @@
         <v>0</v>
       </c>
       <c r="P44" s="11">
-        <v>0.91064314171883898</v>
+        <v>0.97097853058582373</v>
       </c>
       <c r="Q44" s="15">
-        <v>0.91064314171883898</v>
+        <v>0.97097853058582373</v>
       </c>
       <c r="R44" s="12">
         <v>5</v>
@@ -4811,7 +4811,7 @@
         <v>1.1013215859030836</v>
       </c>
       <c r="L45" s="11">
-        <v>0</v>
+        <v>0.91996320147194111</v>
       </c>
       <c r="M45" s="11">
         <v>0</v>
@@ -4823,10 +4823,10 @@
         <v>0</v>
       </c>
       <c r="P45" s="11">
-        <v>0.84460146400976011</v>
+        <v>0.85210107113430378</v>
       </c>
       <c r="Q45" s="15">
-        <v>0.8920917724178502</v>
+        <v>0.86938622754491013</v>
       </c>
       <c r="R45" s="12">
         <v>4</v>
@@ -4879,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="P46" s="11">
-        <v>1.1185167232186137</v>
+        <v>0.94686089454247024</v>
       </c>
       <c r="Q46" s="15">
-        <v>0.8920917724178502</v>
+        <v>0.86938622754491013</v>
       </c>
       <c r="R46" s="12">
         <v>4</v>
@@ -4923,7 +4923,7 @@
         <v>0.42881646655231559</v>
       </c>
       <c r="L47" s="11">
-        <v>0</v>
+        <v>0.41528239202657807</v>
       </c>
       <c r="M47" s="11">
         <v>0</v>
@@ -4935,10 +4935,10 @@
         <v>0</v>
       </c>
       <c r="P47" s="11">
-        <v>0.43453041460708158</v>
+        <v>0.43244580372402625</v>
       </c>
       <c r="Q47" s="15">
-        <v>0.43453041460708158</v>
+        <v>0.43244580372402625</v>
       </c>
       <c r="R47" s="12">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         <v>0.85178875638841567</v>
       </c>
       <c r="L48" s="11">
-        <v>0</v>
+        <v>3.7735849056603774</v>
       </c>
       <c r="M48" s="11">
         <v>0</v>
@@ -4991,10 +4991,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="11">
-        <v>0.91573941134242642</v>
+        <v>1.0454856947061846</v>
       </c>
       <c r="Q48" s="15">
-        <v>0.91573941134242642</v>
+        <v>1.0454856947061846</v>
       </c>
       <c r="R48" s="12">
         <v>5</v>
@@ -5047,10 +5047,10 @@
         <v>0</v>
       </c>
       <c r="P49" s="11">
-        <v>0.62695924764890287</v>
+        <v>0.54555373704309873</v>
       </c>
       <c r="Q49" s="15">
-        <v>0.62695924764890287</v>
+        <v>0.54555373704309873</v>
       </c>
       <c r="R49" s="12">
         <v>0</v>
@@ -5103,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="P50" s="11">
-        <v>0.59382422802850354</v>
+        <v>0.55187637969094927</v>
       </c>
       <c r="Q50" s="15">
-        <v>0.59382422802850354</v>
+        <v>0.55187637969094927</v>
       </c>
       <c r="R50" s="12">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="11">
-        <v>0</v>
+        <v>3.0943025540275051</v>
       </c>
       <c r="M51" s="11">
         <v>0</v>
@@ -5159,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="P51" s="11">
-        <v>0</v>
+        <v>0.26927679945289795</v>
       </c>
       <c r="Q51" s="15">
-        <v>0</v>
+        <v>0.26927679945289795</v>
       </c>
       <c r="R51" s="12">
         <v>0</v>
@@ -5215,10 +5215,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="11">
-        <v>1.1502666527240406</v>
+        <v>1.0472201066260471</v>
       </c>
       <c r="Q52" s="15">
-        <v>1.1502666527240406</v>
+        <v>1.0472201066260471</v>
       </c>
       <c r="R52" s="12">
         <v>5</v>
@@ -5259,7 +5259,7 @@
         <v>0.68634179821551133</v>
       </c>
       <c r="L53" s="11">
-        <v>0</v>
+        <v>1.2330456226880395</v>
       </c>
       <c r="M53" s="11">
         <v>0</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="P53" s="11">
-        <v>1.0874818753020783</v>
+        <v>1.1004732034774953</v>
       </c>
       <c r="Q53" s="15">
-        <v>1.0874818753020783</v>
+        <v>1.1004732034774953</v>
       </c>
       <c r="R53" s="12">
         <v>5</v>
@@ -5327,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="P54" s="11">
-        <v>1.287001287001287</v>
+        <v>1.0209290454313424</v>
       </c>
       <c r="Q54" s="15">
-        <v>1.287001287001287</v>
+        <v>1.0209290454313424</v>
       </c>
       <c r="R54" s="12">
         <v>5</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="P55" s="11">
-        <v>0.60526026191262239</v>
+        <v>0.55365411717334412</v>
       </c>
       <c r="Q55" s="15">
-        <v>0.54261624509558393</v>
+        <v>0.502590272945179</v>
       </c>
       <c r="R55" s="12">
         <v>0</v>
@@ -5439,10 +5439,10 @@
         <v>0</v>
       </c>
       <c r="P56" s="11">
-        <v>0.34578146611341631</v>
+        <v>0.33344448149383127</v>
       </c>
       <c r="Q56" s="15">
-        <v>0.54261624509558393</v>
+        <v>0.502590272945179</v>
       </c>
       <c r="R56" s="12">
         <v>0</v>
@@ -5483,7 +5483,7 @@
         <v>0.8481764206955047</v>
       </c>
       <c r="L57" s="11">
-        <v>0</v>
+        <v>1.1547344110854503</v>
       </c>
       <c r="M57" s="11">
         <v>0</v>
@@ -5495,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="P57" s="11">
-        <v>1.1340929009640666</v>
+        <v>1.135274481938064</v>
       </c>
       <c r="Q57" s="15">
-        <v>1.1340929009640666</v>
+        <v>1.135274481938064</v>
       </c>
       <c r="R57" s="12">
         <v>5</v>
@@ -5539,7 +5539,7 @@
         <v>1.1857707509881423</v>
       </c>
       <c r="L58" s="11">
-        <v>0</v>
+        <v>1.5349194167306217</v>
       </c>
       <c r="M58" s="11">
         <v>0</v>
@@ -5551,10 +5551,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="11">
-        <v>1.0609030197444831</v>
+        <v>1.1363081430838726</v>
       </c>
       <c r="Q58" s="15">
-        <v>1.0609030197444831</v>
+        <v>1.1363081430838726</v>
       </c>
       <c r="R58" s="12">
         <v>5</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="11">
-        <v>0</v>
+        <v>1.9193857965451055</v>
       </c>
       <c r="M59" s="11">
         <v>0</v>
@@ -5607,10 +5607,10 @@
         <v>0</v>
       </c>
       <c r="P59" s="11">
-        <v>0.95829150314867206</v>
+        <v>1.0417534794566214</v>
       </c>
       <c r="Q59" s="15">
-        <v>0.95829150314867206</v>
+        <v>1.0417534794566214</v>
       </c>
       <c r="R59" s="12">
         <v>5</v>
@@ -5651,7 +5651,7 @@
         <v>0.61804697156983934</v>
       </c>
       <c r="L60" s="11">
-        <v>0</v>
+        <v>1.1547344110854503</v>
       </c>
       <c r="M60" s="11">
         <v>0</v>
@@ -5663,10 +5663,10 @@
         <v>0</v>
       </c>
       <c r="P60" s="11">
-        <v>0.9606305208650624</v>
+        <v>0.98324811625403663</v>
       </c>
       <c r="Q60" s="15">
-        <v>0.9606305208650624</v>
+        <v>0.98324811625403663</v>
       </c>
       <c r="R60" s="12">
         <v>5</v>
@@ -5719,10 +5719,10 @@
         <v>0</v>
       </c>
       <c r="P61" s="11">
-        <v>1.1127596439169138</v>
+        <v>1.0582010582010581</v>
       </c>
       <c r="Q61" s="15">
-        <v>1.1127596439169138</v>
+        <v>1.0582010582010581</v>
       </c>
       <c r="R61" s="12">
         <v>5</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="11">
-        <v>0</v>
+        <v>2.4330900243309004</v>
       </c>
       <c r="M62" s="11">
         <v>0</v>
@@ -5775,10 +5775,10 @@
         <v>0</v>
       </c>
       <c r="P62" s="11">
-        <v>1.0802246867348408</v>
+        <v>1.1558335599673648</v>
       </c>
       <c r="Q62" s="15">
-        <v>1.0802246867348408</v>
+        <v>1.1558335599673648</v>
       </c>
       <c r="R62" s="12">
         <v>5</v>
@@ -5819,7 +5819,7 @@
         <v>1.4381591562799616</v>
       </c>
       <c r="L63" s="11">
-        <v>0</v>
+        <v>1.0183299389002036</v>
       </c>
       <c r="M63" s="11">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P63" s="11">
-        <v>0.86248203162434112</v>
+        <v>0.86948563060589423</v>
       </c>
       <c r="Q63" s="15">
-        <v>0.86248203162434112</v>
+        <v>0.86948563060589423</v>
       </c>
       <c r="R63" s="12">
         <v>4</v>
@@ -5887,10 +5887,10 @@
         <v>0</v>
       </c>
       <c r="P64" s="11">
-        <v>1.2443828639904133</v>
+        <v>1.1161494021228</v>
       </c>
       <c r="Q64" s="15">
-        <v>1.1998203551440614</v>
+        <v>1.1116019310257785</v>
       </c>
       <c r="R64" s="12">
         <v>5</v>
@@ -5931,7 +5931,7 @@
         <v>0.87565674255691772</v>
       </c>
       <c r="L65" s="11">
-        <v>0</v>
+        <v>0.33921302578018997</v>
       </c>
       <c r="M65" s="11">
         <v>0</v>
@@ -5943,10 +5943,10 @@
         <v>0</v>
       </c>
       <c r="P65" s="11">
-        <v>1.3063217826641798</v>
+        <v>1.1840751222022126</v>
       </c>
       <c r="Q65" s="15">
-        <v>1.1998203551440614</v>
+        <v>1.1116019310257785</v>
       </c>
       <c r="R65" s="12">
         <v>5</v>
@@ -5999,10 +5999,10 @@
         <v>0</v>
       </c>
       <c r="P66" s="11">
-        <v>1.0467220807078697</v>
+        <v>0.98804100227790437</v>
       </c>
       <c r="Q66" s="15">
-        <v>1.1998203551440614</v>
+        <v>1.1116019310257785</v>
       </c>
       <c r="R66" s="12">
         <v>5</v>
@@ -6055,10 +6055,10 @@
         <v>0</v>
       </c>
       <c r="P67" s="11">
-        <v>1.1478157439446366</v>
+        <v>1.1323874546618307</v>
       </c>
       <c r="Q67" s="15">
-        <v>1.1998203551440614</v>
+        <v>1.1116019310257785</v>
       </c>
       <c r="R67" s="12">
         <v>5</v>
@@ -6099,7 +6099,7 @@
         <v>1.7793594306049823</v>
       </c>
       <c r="L68" s="11">
-        <v>0</v>
+        <v>1.8639328984156571</v>
       </c>
       <c r="M68" s="11">
         <v>0</v>
@@ -6111,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="P68" s="11">
-        <v>1.4503583645544877</v>
+        <v>1.4835967343270167</v>
       </c>
       <c r="Q68" s="15">
-        <v>1.3651150489288548</v>
+        <v>1.4057239057239057</v>
       </c>
       <c r="R68" s="12">
         <v>5</v>
@@ -6155,7 +6155,7 @@
         <v>0.75872534142640369</v>
       </c>
       <c r="L69" s="11">
-        <v>0</v>
+        <v>1.941747572815534</v>
       </c>
       <c r="M69" s="11">
         <v>0</v>
@@ -6167,10 +6167,10 @@
         <v>0</v>
       </c>
       <c r="P69" s="11">
-        <v>1.2071827372868569</v>
+        <v>1.2601512181461776</v>
       </c>
       <c r="Q69" s="15">
-        <v>1.3651150489288548</v>
+        <v>1.4057239057239057</v>
       </c>
       <c r="R69" s="12">
         <v>5</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="P70" s="11">
-        <v>0.75849514563106801</v>
+        <v>0.72046109510086453</v>
       </c>
       <c r="Q70" s="15">
-        <v>0.75849514563106801</v>
+        <v>0.72046109510086453</v>
       </c>
       <c r="R70" s="12">
         <v>0</v>
@@ -6279,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="P71" s="11">
-        <v>1.3698630136986301</v>
+        <v>1.3245033112582782</v>
       </c>
       <c r="Q71" s="15">
-        <v>1.3698630136986301</v>
+        <v>1.3245033112582782</v>
       </c>
       <c r="R71" s="12">
         <v>5</v>
@@ -6323,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="11">
-        <v>0</v>
+        <v>3.7243947858472999</v>
       </c>
       <c r="M72" s="11">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="P72" s="11">
-        <v>1.4478764478764479</v>
+        <v>1.7832647462277091</v>
       </c>
       <c r="Q72" s="15">
-        <v>1.4478764478764479</v>
+        <v>1.7832647462277091</v>
       </c>
       <c r="R72" s="12">
         <v>5</v>
@@ -6379,7 +6379,7 @@
         <v>0.1817520901490367</v>
       </c>
       <c r="L73" s="11">
-        <v>0</v>
+        <v>0.21477663230240548</v>
       </c>
       <c r="M73" s="11">
         <v>0</v>
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="P73" s="11">
-        <v>0.21491510853212981</v>
+        <v>0.21488739900292247</v>
       </c>
       <c r="Q73" s="15">
-        <v>0.3314407585670231</v>
+        <v>0.33220044463751819</v>
       </c>
       <c r="R73" s="12">
         <v>0</v>
@@ -6435,7 +6435,7 @@
         <v>3.0120481927710845</v>
       </c>
       <c r="L74" s="11">
-        <v>0</v>
+        <v>6.3291139240506329</v>
       </c>
       <c r="M74" s="11">
         <v>0</v>
@@ -6447,10 +6447,10 @@
         <v>0</v>
       </c>
       <c r="P74" s="11">
-        <v>0.89245872378402502</v>
+        <v>0.95560129373713609</v>
       </c>
       <c r="Q74" s="15">
-        <v>0.3314407585670231</v>
+        <v>0.33220044463751819</v>
       </c>
       <c r="R74" s="12">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0.53590568060021437</v>
       </c>
       <c r="L75" s="11">
-        <v>0</v>
+        <v>0.44404973357015987</v>
       </c>
       <c r="M75" s="11">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         <v>0</v>
       </c>
       <c r="P75" s="11">
-        <v>0.23463162834350071</v>
+        <v>0.25906735751295334</v>
       </c>
       <c r="Q75" s="15">
-        <v>0.3314407585670231</v>
+        <v>0.33220044463751819</v>
       </c>
       <c r="R75" s="12">
         <v>0</v>
@@ -6562,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="15">
-        <v>0.3314407585670231</v>
+        <v>0.33220044463751819</v>
       </c>
       <c r="R76" s="12">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0.27834477639636296</v>
       </c>
       <c r="Q77" s="15">
-        <v>0.3314407585670231</v>
+        <v>0.33220044463751819</v>
       </c>
       <c r="R77" s="12">
         <v>0</v>
@@ -6674,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="15">
-        <v>0.3314407585670231</v>
+        <v>0.33220044463751819</v>
       </c>
       <c r="R78" s="12">
         <v>0</v>
@@ -6730,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="15">
-        <v>0.3314407585670231</v>
+        <v>0.33220044463751819</v>
       </c>
       <c r="R79" s="12">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="11">
-        <v>0</v>
+        <v>2.3980815347721824</v>
       </c>
       <c r="M80" s="11">
         <v>0</v>
@@ -6783,10 +6783,10 @@
         <v>0</v>
       </c>
       <c r="P80" s="11">
-        <v>0.53078556263269638</v>
+        <v>0.77089115016959608</v>
       </c>
       <c r="Q80" s="15">
-        <v>0.53078556263269638</v>
+        <v>0.77089115016959608</v>
       </c>
       <c r="R80" s="12">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>1.1746280344557556</v>
       </c>
       <c r="L81" s="11">
-        <v>0</v>
+        <v>1.0305028854080791</v>
       </c>
       <c r="M81" s="11">
         <v>0</v>
@@ -6839,10 +6839,10 @@
         <v>0</v>
       </c>
       <c r="P81" s="11">
-        <v>1.050297584315556</v>
+        <v>1.0478429768963402</v>
       </c>
       <c r="Q81" s="15">
-        <v>1.0646489971346704</v>
+        <v>1.0756076624198065</v>
       </c>
       <c r="R81" s="12">
         <v>5</v>
@@ -6883,7 +6883,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="11">
-        <v>0</v>
+        <v>3.0487804878048781</v>
       </c>
       <c r="M82" s="11">
         <v>0</v>
@@ -6895,10 +6895,10 @@
         <v>0</v>
       </c>
       <c r="P82" s="11">
-        <v>1.1668744804655029</v>
+        <v>1.2869649805447472</v>
       </c>
       <c r="Q82" s="15">
-        <v>1.0646489971346704</v>
+        <v>1.0756076624198065</v>
       </c>
       <c r="R82" s="12">
         <v>5</v>
@@ -6939,7 +6939,7 @@
         <v>1.0172939979654121</v>
       </c>
       <c r="L83" s="11">
-        <v>0</v>
+        <v>1.9083969465648856</v>
       </c>
       <c r="M83" s="11">
         <v>0</v>
@@ -6951,10 +6951,10 @@
         <v>0</v>
       </c>
       <c r="P83" s="11">
-        <v>1.2977505319687912</v>
+        <v>1.3135425920442207</v>
       </c>
       <c r="Q83" s="15">
-        <v>1.2794886283373357</v>
+        <v>1.263661665874686</v>
       </c>
       <c r="R83" s="12">
         <v>5</v>
@@ -7007,10 +7007,10 @@
         <v>0</v>
       </c>
       <c r="P84" s="11">
-        <v>1.2374679412450456</v>
+        <v>1.1538043478260869</v>
       </c>
       <c r="Q84" s="15">
-        <v>1.2794886283373357</v>
+        <v>1.263661665874686</v>
       </c>
       <c r="R84" s="12">
         <v>5</v>
@@ -7051,7 +7051,7 @@
         <v>0.77639751552795033</v>
       </c>
       <c r="L85" s="11">
-        <v>0</v>
+        <v>3.1446540880503147</v>
       </c>
       <c r="M85" s="11">
         <v>0</v>
@@ -7063,10 +7063,10 @@
         <v>0</v>
       </c>
       <c r="P85" s="11">
-        <v>1.4279885760913913</v>
+        <v>1.5325670498084292</v>
       </c>
       <c r="Q85" s="15">
-        <v>1.4279885760913913</v>
+        <v>1.5325670498084292</v>
       </c>
       <c r="R85" s="12">
         <v>5</v>
@@ -7107,7 +7107,7 @@
         <v>1.6051364365971108</v>
       </c>
       <c r="L86" s="11">
-        <v>0</v>
+        <v>1.2618296529968454</v>
       </c>
       <c r="M86" s="11">
         <v>0</v>
@@ -7119,10 +7119,10 @@
         <v>0</v>
       </c>
       <c r="P86" s="11">
-        <v>1.3294657964708727</v>
+        <v>1.3185921493052033</v>
       </c>
       <c r="Q86" s="15">
-        <v>1.4389092229890197</v>
+        <v>1.4284342440101792</v>
       </c>
       <c r="R86" s="12">
         <v>5</v>
@@ -7163,7 +7163,7 @@
         <v>1.8484288354898337</v>
       </c>
       <c r="L87" s="11">
-        <v>0</v>
+        <v>1.7642907551164433</v>
       </c>
       <c r="M87" s="11">
         <v>0</v>
@@ -7175,10 +7175,10 @@
         <v>0</v>
       </c>
       <c r="P87" s="11">
-        <v>2.068159338189012</v>
+        <v>2.0338171957249962</v>
       </c>
       <c r="Q87" s="15">
-        <v>1.4389092229890197</v>
+        <v>1.4284342440101792</v>
       </c>
       <c r="R87" s="12">
         <v>5</v>
@@ -7219,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="11">
-        <v>0</v>
+        <v>1.1261261261261262</v>
       </c>
       <c r="M88" s="11">
         <v>0</v>
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="P88" s="11">
-        <v>0.96765275089853475</v>
+        <v>0.98497906919477962</v>
       </c>
       <c r="Q88" s="15">
-        <v>1.4389092229890197</v>
+        <v>1.4284342440101792</v>
       </c>
       <c r="R88" s="12">
         <v>5</v>
@@ -7290,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="15">
-        <v>1.4389092229890197</v>
+        <v>1.4284342440101792</v>
       </c>
       <c r="R89" s="12">
         <v>5</v>
@@ -7331,7 +7331,7 @@
         <v>1.3755158184319121</v>
       </c>
       <c r="L90" s="11">
-        <v>0</v>
+        <v>1.2412081092263136</v>
       </c>
       <c r="M90" s="11">
         <v>0</v>
@@ -7343,10 +7343,10 @@
         <v>0</v>
       </c>
       <c r="P90" s="11">
-        <v>1.0955473824242898</v>
+        <v>1.1187154514345881</v>
       </c>
       <c r="Q90" s="15">
-        <v>1.4389092229890197</v>
+        <v>1.4284342440101792</v>
       </c>
       <c r="R90" s="12">
         <v>5</v>
@@ -7387,7 +7387,7 @@
         <v>0.88752622236566081</v>
       </c>
       <c r="L91" s="11">
-        <v>0</v>
+        <v>0.61425061425061422</v>
       </c>
       <c r="M91" s="11">
         <v>0</v>
@@ -7399,10 +7399,10 @@
         <v>0</v>
       </c>
       <c r="P91" s="11">
-        <v>0.96583363515634435</v>
+        <v>0.92331203701738374</v>
       </c>
       <c r="Q91" s="15">
-        <v>0.97328069047837662</v>
+        <v>0.94224677118024536</v>
       </c>
       <c r="R91" s="12">
         <v>5</v>
@@ -7443,7 +7443,7 @@
         <v>0.52356020942408377</v>
       </c>
       <c r="L92" s="11">
-        <v>0</v>
+        <v>1.0699001426533523</v>
       </c>
       <c r="M92" s="11">
         <v>0</v>
@@ -7455,10 +7455,10 @@
         <v>0</v>
       </c>
       <c r="P92" s="11">
-        <v>0.99693251533742333</v>
+        <v>1.0040160642570282</v>
       </c>
       <c r="Q92" s="15">
-        <v>0.97328069047837662</v>
+        <v>0.94224677118024536</v>
       </c>
       <c r="R92" s="12">
         <v>5</v>
@@ -7499,7 +7499,7 @@
         <v>1.1834319526627219</v>
       </c>
       <c r="L93" s="11">
-        <v>0</v>
+        <v>2.7932960893854748</v>
       </c>
       <c r="M93" s="11">
         <v>0</v>
@@ -7511,10 +7511,10 @@
         <v>0</v>
       </c>
       <c r="P93" s="11">
-        <v>1.6054588320638374</v>
+        <v>1.7214433777001963</v>
       </c>
       <c r="Q93" s="15">
-        <v>1.2902254942816131</v>
+        <v>1.3437870548309276</v>
       </c>
       <c r="R93" s="12">
         <v>5</v>
@@ -7567,10 +7567,10 @@
         <v>0</v>
       </c>
       <c r="P94" s="11">
-        <v>0.25865479723046486</v>
+        <v>0.21346938775510205</v>
       </c>
       <c r="Q94" s="15">
-        <v>1.2902254942816131</v>
+        <v>1.3437870548309276</v>
       </c>
       <c r="R94" s="12">
         <v>5</v>
@@ -7611,7 +7611,7 @@
         <v>1.4727540500736378</v>
       </c>
       <c r="L95" s="11">
-        <v>0</v>
+        <v>0.71123755334281646</v>
       </c>
       <c r="M95" s="11">
         <v>0</v>
@@ -7623,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="P95" s="11">
-        <v>1.3203613620569841</v>
+        <v>1.2661433274246645</v>
       </c>
       <c r="Q95" s="15">
-        <v>1.2360446570972887</v>
+        <v>1.1742257448994569</v>
       </c>
       <c r="R95" s="12">
         <v>5</v>
@@ -7679,10 +7679,10 @@
         <v>0</v>
       </c>
       <c r="P96" s="11">
-        <v>1.1225444340505144</v>
+        <v>1.0474860335195531</v>
       </c>
       <c r="Q96" s="15">
-        <v>1.2360446570972887</v>
+        <v>1.1742257448994569</v>
       </c>
       <c r="R96" s="12">
         <v>5</v>
@@ -7723,7 +7723,7 @@
         <v>1.5278838808250572</v>
       </c>
       <c r="L97" s="11">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M97" s="11">
         <v>0</v>
@@ -7735,10 +7735,10 @@
         <v>0</v>
       </c>
       <c r="P97" s="11">
-        <v>1.2033185640654671</v>
+        <v>1.1569884364002012</v>
       </c>
       <c r="Q97" s="15">
-        <v>1.2033185640654671</v>
+        <v>1.1569884364002012</v>
       </c>
       <c r="R97" s="12">
         <v>5</v>
@@ -7779,7 +7779,7 @@
         <v>1.5</v>
       </c>
       <c r="L98" s="11">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="M98" s="11">
         <v>0</v>
@@ -7791,10 +7791,10 @@
         <v>0</v>
       </c>
       <c r="P98" s="11">
-        <v>1.3682230203523174</v>
+        <v>1.3956221536653446</v>
       </c>
       <c r="Q98" s="15">
-        <v>1.3682230203523174</v>
+        <v>1.3956221536653446</v>
       </c>
       <c r="R98" s="12">
         <v>5</v>
@@ -7835,7 +7835,7 @@
         <v>1.5022533800701052</v>
       </c>
       <c r="L99" s="11">
-        <v>0</v>
+        <v>0.67385444743935308</v>
       </c>
       <c r="M99" s="11">
         <v>0</v>
@@ -7847,10 +7847,10 @@
         <v>0</v>
       </c>
       <c r="P99" s="11">
-        <v>0.90210685601210572</v>
+        <v>0.88396014143362267</v>
       </c>
       <c r="Q99" s="15">
-        <v>1.0159821812355907</v>
+        <v>0.99583559659605292</v>
       </c>
       <c r="R99" s="12">
         <v>5</v>
@@ -7891,7 +7891,7 @@
         <v>1.1013215859030836</v>
       </c>
       <c r="L100" s="11">
-        <v>0</v>
+        <v>0.92592592592592593</v>
       </c>
       <c r="M100" s="11">
         <v>0</v>
@@ -7903,10 +7903,10 @@
         <v>0</v>
       </c>
       <c r="P100" s="11">
-        <v>1.2486621476988939</v>
+        <v>1.2291876187283495</v>
       </c>
       <c r="Q100" s="15">
-        <v>1.0159821812355907</v>
+        <v>0.99583559659605292</v>
       </c>
       <c r="R100" s="12">
         <v>5</v>
@@ -7947,7 +7947,7 @@
         <v>0</v>
       </c>
       <c r="L101" s="11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M101" s="11">
         <v>0</v>
@@ -7959,10 +7959,10 @@
         <v>0</v>
       </c>
       <c r="P101" s="11">
-        <v>1.1279407025459234</v>
+        <v>1.3502565487442615</v>
       </c>
       <c r="Q101" s="15">
-        <v>1.1658031088082901</v>
+        <v>1.3109023377758358</v>
       </c>
       <c r="R101" s="12">
         <v>5</v>
@@ -8015,10 +8015,10 @@
         <v>0</v>
       </c>
       <c r="P102" s="11">
-        <v>1.321003963011889</v>
+        <v>1.1441647597254005</v>
       </c>
       <c r="Q102" s="15">
-        <v>1.1658031088082901</v>
+        <v>1.3109023377758358</v>
       </c>
       <c r="R102" s="12">
         <v>5</v>
@@ -8059,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="L103" s="11">
-        <v>0</v>
+        <v>2.4539877300613497</v>
       </c>
       <c r="M103" s="11">
         <v>0</v>
@@ -8071,10 +8071,10 @@
         <v>0</v>
       </c>
       <c r="P103" s="11">
-        <v>1.1680786445012787</v>
+        <v>1.3162918964785744</v>
       </c>
       <c r="Q103" s="15">
-        <v>1.1680786445012787</v>
+        <v>1.3162918964785744</v>
       </c>
       <c r="R103" s="12">
         <v>5</v>
@@ -8115,7 +8115,7 @@
         <v>1.0040160642570282</v>
       </c>
       <c r="L104" s="11">
-        <v>0</v>
+        <v>2.0585544373284539</v>
       </c>
       <c r="M104" s="11">
         <v>0</v>
@@ -8127,10 +8127,10 @@
         <v>0</v>
       </c>
       <c r="P104" s="11">
-        <v>1.6130163405568414</v>
+        <v>1.6722408026755853</v>
       </c>
       <c r="Q104" s="15">
-        <v>1.6130163405568414</v>
+        <v>1.6722408026755853</v>
       </c>
       <c r="R104" s="12">
         <v>5</v>
@@ -8171,7 +8171,7 @@
         <v>0.64850843060959795</v>
       </c>
       <c r="L105" s="11">
-        <v>0</v>
+        <v>5.0890585241730282</v>
       </c>
       <c r="M105" s="11">
         <v>0</v>
@@ -8183,10 +8183,10 @@
         <v>0</v>
       </c>
       <c r="P105" s="11">
-        <v>1.3087227018791265</v>
+        <v>1.4883903736848469</v>
       </c>
       <c r="Q105" s="15">
-        <v>1.2915541047576167</v>
+        <v>1.3414574182128105</v>
       </c>
       <c r="R105" s="12">
         <v>5</v>
@@ -8227,7 +8227,7 @@
         <v>1.5262515262515262</v>
       </c>
       <c r="L106" s="11">
-        <v>0</v>
+        <v>1.2933264355923435</v>
       </c>
       <c r="M106" s="11">
         <v>0</v>
@@ -8239,10 +8239,10 @@
         <v>0</v>
       </c>
       <c r="P106" s="11">
-        <v>1.1639286275742808</v>
+        <v>1.1809962470146707</v>
       </c>
       <c r="Q106" s="15">
-        <v>1.2915541047576167</v>
+        <v>1.3414574182128105</v>
       </c>
       <c r="R106" s="12">
         <v>5</v>
@@ -8295,10 +8295,10 @@
         <v>0</v>
       </c>
       <c r="P107" s="11">
-        <v>1.4495379597753215</v>
+        <v>1.3644891693672181</v>
       </c>
       <c r="Q107" s="15">
-        <v>1.2915541047576167</v>
+        <v>1.3414574182128105</v>
       </c>
       <c r="R107" s="12">
         <v>5</v>
@@ -8339,7 +8339,7 @@
         <v>2.3041474654377878</v>
       </c>
       <c r="L108" s="11">
-        <v>0</v>
+        <v>1.6891891891891893</v>
       </c>
       <c r="M108" s="11">
         <v>0</v>
@@ -8351,10 +8351,10 @@
         <v>0</v>
       </c>
       <c r="P108" s="11">
-        <v>2.44392523364486</v>
+        <v>1.9240837696335078</v>
       </c>
       <c r="Q108" s="15">
-        <v>1.2915541047576167</v>
+        <v>1.3414574182128105</v>
       </c>
       <c r="R108" s="12">
         <v>5</v>
@@ -8395,7 +8395,7 @@
         <v>1.6920473773265652</v>
       </c>
       <c r="L109" s="11">
-        <v>0</v>
+        <v>1.0141987829614605</v>
       </c>
       <c r="M109" s="11">
         <v>0</v>
@@ -8407,10 +8407,10 @@
         <v>0</v>
       </c>
       <c r="P109" s="11">
-        <v>1.1455763130066972</v>
+        <v>1.1350737797956867</v>
       </c>
       <c r="Q109" s="15">
-        <v>1.1455763130066972</v>
+        <v>1.1350737797956867</v>
       </c>
       <c r="R109" s="12">
         <v>5</v>
@@ -8451,7 +8451,7 @@
         <v>2.1253985122210413</v>
       </c>
       <c r="L110" s="11">
-        <v>0</v>
+        <v>3.7383177570093458</v>
       </c>
       <c r="M110" s="11">
         <v>0</v>
@@ -8463,13 +8463,13 @@
         <v>0</v>
       </c>
       <c r="P110" s="11">
-        <v>0.69942297604476311</v>
+        <v>0.83521256159692647</v>
       </c>
       <c r="Q110" s="15">
-        <v>0.69942297604476311</v>
+        <v>0.83521256159692647</v>
       </c>
       <c r="R110" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -8507,7 +8507,7 @@
         <v>1.1474469305794608</v>
       </c>
       <c r="L111" s="11">
-        <v>0</v>
+        <v>1.6713091922005572</v>
       </c>
       <c r="M111" s="11">
         <v>0</v>
@@ -8519,10 +8519,10 @@
         <v>0</v>
       </c>
       <c r="P111" s="11">
-        <v>1.2604730481204123</v>
+        <v>1.3087292239235702</v>
       </c>
       <c r="Q111" s="15">
-        <v>1.3359583743495993</v>
+        <v>1.3629042250030976</v>
       </c>
       <c r="R111" s="12">
         <v>5</v>
@@ -8575,10 +8575,10 @@
         <v>0</v>
       </c>
       <c r="P112" s="11">
-        <v>2.7210884353741496</v>
+        <v>2.3255813953488373</v>
       </c>
       <c r="Q112" s="15">
-        <v>1.3359583743495993</v>
+        <v>1.3629042250030976</v>
       </c>
       <c r="R112" s="12">
         <v>5</v>
@@ -8619,7 +8619,7 @@
         <v>1.3986013986013985</v>
       </c>
       <c r="L113" s="11">
-        <v>0</v>
+        <v>0.43936731107205623</v>
       </c>
       <c r="M113" s="11">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="P113" s="11">
-        <v>1.218478491205764</v>
+        <v>1.1741780753472568</v>
       </c>
       <c r="Q113" s="15">
-        <v>1.218478491205764</v>
+        <v>1.1741780753472568</v>
       </c>
       <c r="R113" s="12">
         <v>5</v>
@@ -8675,7 +8675,7 @@
         <v>1.2201073694485114</v>
       </c>
       <c r="L114" s="11">
-        <v>0</v>
+        <v>1.2812299807815504</v>
       </c>
       <c r="M114" s="11">
         <v>0</v>
@@ -8687,10 +8687,10 @@
         <v>0</v>
       </c>
       <c r="P114" s="11">
-        <v>1.1910777448928029</v>
+        <v>1.2002076034773583</v>
       </c>
       <c r="Q114" s="15">
-        <v>1.1910777448928029</v>
+        <v>1.2002076034773583</v>
       </c>
       <c r="R114" s="12">
         <v>5</v>
@@ -8731,7 +8731,7 @@
         <v>0.85836909871244638</v>
       </c>
       <c r="L115" s="11">
-        <v>0</v>
+        <v>1.2642225031605563</v>
       </c>
       <c r="M115" s="11">
         <v>0</v>
@@ -8743,10 +8743,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="11">
-        <v>0.93325609834588397</v>
+        <v>0.96384134587300663</v>
       </c>
       <c r="Q115" s="15">
-        <v>1.0499865386341201</v>
+        <v>1.0651689745327781</v>
       </c>
       <c r="R115" s="12">
         <v>5</v>
@@ -8787,7 +8787,7 @@
         <v>1.8315018315018314</v>
       </c>
       <c r="L116" s="11">
-        <v>0</v>
+        <v>1.3774104683195592</v>
       </c>
       <c r="M116" s="11">
         <v>0</v>
@@ -8799,10 +8799,10 @@
         <v>0</v>
       </c>
       <c r="P116" s="11">
-        <v>1.5787396395211157</v>
+        <v>1.5611865017413233</v>
       </c>
       <c r="Q116" s="15">
-        <v>1.5787396395211157</v>
+        <v>1.5611865017413233</v>
       </c>
       <c r="R116" s="12">
         <v>5</v>
@@ -8843,7 +8843,7 @@
         <v>1.1695906432748537</v>
       </c>
       <c r="L117" s="11">
-        <v>0</v>
+        <v>0.86580086580086579</v>
       </c>
       <c r="M117" s="11">
         <v>0</v>
@@ -8855,10 +8855,10 @@
         <v>0</v>
       </c>
       <c r="P117" s="11">
-        <v>1.0767468499427262</v>
+        <v>1.0565568676196395</v>
       </c>
       <c r="Q117" s="15">
-        <v>1.0767468499427262</v>
+        <v>1.0565568676196395</v>
       </c>
       <c r="R117" s="12">
         <v>5</v>
@@ -8899,7 +8899,7 @@
         <v>1.4858841010401189</v>
       </c>
       <c r="L118" s="11">
-        <v>0</v>
+        <v>1.1074197120708749</v>
       </c>
       <c r="M118" s="11">
         <v>0</v>
@@ -8911,10 +8911,10 @@
         <v>0</v>
       </c>
       <c r="P118" s="11">
-        <v>1.1977531802412027</v>
+        <v>1.1860264519838988</v>
       </c>
       <c r="Q118" s="15">
-        <v>1.1084640328237707</v>
+        <v>1.1565836298932384</v>
       </c>
       <c r="R118" s="12">
         <v>5</v>
@@ -8955,7 +8955,7 @@
         <v>1.2254901960784315</v>
       </c>
       <c r="L119" s="11">
-        <v>0</v>
+        <v>2.6385224274406331</v>
       </c>
       <c r="M119" s="11">
         <v>0</v>
@@ -8967,10 +8967,10 @@
         <v>0</v>
       </c>
       <c r="P119" s="11">
-        <v>1.0288065843621399</v>
+        <v>1.190161332980693</v>
       </c>
       <c r="Q119" s="15">
-        <v>1.1084640328237707</v>
+        <v>1.1565836298932384</v>
       </c>
       <c r="R119" s="12">
         <v>5</v>
@@ -9011,7 +9011,7 @@
         <v>0.71890726096333568</v>
       </c>
       <c r="L120" s="11">
-        <v>0</v>
+        <v>1.540041067761807</v>
       </c>
       <c r="M120" s="11">
         <v>0</v>
@@ -9023,10 +9023,10 @@
         <v>0</v>
       </c>
       <c r="P120" s="11">
-        <v>1.0530983261279236</v>
+        <v>1.1005502751375689</v>
       </c>
       <c r="Q120" s="15">
-        <v>1.1084640328237707</v>
+        <v>1.1565836298932384</v>
       </c>
       <c r="R120" s="12">
         <v>5</v>
@@ -9067,7 +9067,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="L121" s="11">
-        <v>0</v>
+        <v>2.9498525073746311</v>
       </c>
       <c r="M121" s="11">
         <v>0</v>
@@ -9079,10 +9079,10 @@
         <v>0</v>
       </c>
       <c r="P121" s="11">
-        <v>1.0539258738802038</v>
+        <v>1.1604774535809019</v>
       </c>
       <c r="Q121" s="15">
-        <v>1.1084640328237707</v>
+        <v>1.1565836298932384</v>
       </c>
       <c r="R121" s="12">
         <v>5</v>
@@ -9123,7 +9123,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="11">
-        <v>0</v>
+        <v>3.9682539682539684</v>
       </c>
       <c r="M122" s="11">
         <v>0</v>
@@ -9135,10 +9135,10 @@
         <v>0</v>
       </c>
       <c r="P122" s="11">
-        <v>1.1848341232227488</v>
+        <v>1.3167795334838224</v>
       </c>
       <c r="Q122" s="15">
-        <v>1.1848341232227488</v>
+        <v>1.3167795334838224</v>
       </c>
       <c r="R122" s="12">
         <v>5</v>
@@ -9179,7 +9179,7 @@
         <v>1.9305019305019304</v>
       </c>
       <c r="L123" s="11">
-        <v>0</v>
+        <v>2.9761904761904763</v>
       </c>
       <c r="M123" s="11">
         <v>0</v>
@@ -9191,13 +9191,13 @@
         <v>0</v>
       </c>
       <c r="P123" s="11">
-        <v>0.73340667400073345</v>
+        <v>0.86355785837651122</v>
       </c>
       <c r="Q123" s="15">
-        <v>0.73340667400073345</v>
+        <v>0.86355785837651122</v>
       </c>
       <c r="R123" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -9250,7 +9250,7 @@
         <v>1.2765957446808511</v>
       </c>
       <c r="Q124" s="15">
-        <v>1.3867002836432398</v>
+        <v>1.1417761713339865</v>
       </c>
       <c r="R124" s="12">
         <v>5</v>
@@ -9291,7 +9291,7 @@
         <v>0.94043887147335425</v>
       </c>
       <c r="L125" s="11">
-        <v>0</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="M125" s="11">
         <v>0</v>
@@ -9303,10 +9303,10 @@
         <v>0</v>
       </c>
       <c r="P125" s="11">
-        <v>1.0076412797044252</v>
+        <v>0.99739143777811878</v>
       </c>
       <c r="Q125" s="15">
-        <v>1.3867002836432398</v>
+        <v>1.1417761713339865</v>
       </c>
       <c r="R125" s="12">
         <v>5</v>
@@ -9347,7 +9347,7 @@
         <v>1.4204545454545454</v>
       </c>
       <c r="L126" s="11">
-        <v>0</v>
+        <v>1.5723270440251573</v>
       </c>
       <c r="M126" s="11">
         <v>0</v>
@@ -9359,10 +9359,10 @@
         <v>0</v>
       </c>
       <c r="P126" s="11">
-        <v>1.3129102844638949</v>
+        <v>1.3244109856405968</v>
       </c>
       <c r="Q126" s="15">
-        <v>1.3867002836432398</v>
+        <v>1.1417761713339865</v>
       </c>
       <c r="R126" s="12">
         <v>5</v>
@@ -9403,7 +9403,7 @@
         <v>1.4577259475218658</v>
       </c>
       <c r="L127" s="11">
-        <v>0</v>
+        <v>2.2727272727272729</v>
       </c>
       <c r="M127" s="11">
         <v>0</v>
@@ -9415,10 +9415,10 @@
         <v>0</v>
       </c>
       <c r="P127" s="11">
-        <v>1.4009962640099627</v>
+        <v>1.4568764568764569</v>
       </c>
       <c r="Q127" s="15">
-        <v>1.3867002836432398</v>
+        <v>1.1417761713339865</v>
       </c>
       <c r="R127" s="12">
         <v>5</v>
@@ -9435,22 +9435,22 @@
         <v>598</v>
       </c>
       <c r="D128" s="11">
-        <v>0</v>
+        <v>0.85034013605442171</v>
       </c>
       <c r="E128" s="11">
-        <v>0</v>
+        <v>1.5600624024960998</v>
       </c>
       <c r="F128" s="11">
-        <v>0</v>
+        <v>1.1380880121396055</v>
       </c>
       <c r="G128" s="11">
-        <v>0</v>
+        <v>1.567398119122257</v>
       </c>
       <c r="H128" s="11">
         <v>0</v>
       </c>
       <c r="I128" s="11">
-        <v>0</v>
+        <v>2.109704641350211</v>
       </c>
       <c r="J128" s="11">
         <v>0</v>
@@ -9459,7 +9459,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="11">
-        <v>0</v>
+        <v>2.808988764044944</v>
       </c>
       <c r="M128" s="11">
         <v>0</v>
@@ -9471,10 +9471,10 @@
         <v>0</v>
       </c>
       <c r="P128" s="11">
-        <v>0</v>
+        <v>1.0473031942747426</v>
       </c>
       <c r="Q128" s="15">
-        <v>1.3867002836432398</v>
+        <v>1.1417761713339865</v>
       </c>
       <c r="R128" s="12">
         <v>5</v>
@@ -9527,10 +9527,10 @@
         <v>0</v>
       </c>
       <c r="P129" s="11">
-        <v>1.09838380668445</v>
+        <v>1.0617321401486426</v>
       </c>
       <c r="Q129" s="15">
-        <v>1.0586655649659162</v>
+        <v>1.0480136485498415</v>
       </c>
       <c r="R129" s="12">
         <v>5</v>
@@ -9571,7 +9571,7 @@
         <v>0.41322314049586778</v>
       </c>
       <c r="L130" s="11">
-        <v>0</v>
+        <v>1.2531328320802004</v>
       </c>
       <c r="M130" s="11">
         <v>0</v>
@@ -9583,10 +9583,10 @@
         <v>0</v>
       </c>
       <c r="P130" s="11">
-        <v>1.0086746015735324</v>
+        <v>1.0268857356235996</v>
       </c>
       <c r="Q130" s="15">
-        <v>1.0586655649659162</v>
+        <v>1.0480136485498415</v>
       </c>
       <c r="R130" s="12">
         <v>5</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="P131" s="11">
-        <v>1.1374715632109198</v>
+        <v>1.0903426791277258</v>
       </c>
       <c r="Q131" s="15">
-        <v>1.0586655649659162</v>
+        <v>1.0480136485498415</v>
       </c>
       <c r="R131" s="12">
         <v>5</v>
@@ -9683,7 +9683,7 @@
         <v>0.76923076923076927</v>
       </c>
       <c r="L132" s="11">
-        <v>0</v>
+        <v>1.2437810945273631</v>
       </c>
       <c r="M132" s="11">
         <v>0</v>
@@ -9695,10 +9695,10 @@
         <v>0</v>
       </c>
       <c r="P132" s="11">
-        <v>1.0917030567685591</v>
+        <v>1.1093961026432568</v>
       </c>
       <c r="Q132" s="15">
-        <v>1.0917030567685591</v>
+        <v>1.1093961026432568</v>
       </c>
       <c r="R132" s="12">
         <v>5</v>
@@ -9739,7 +9739,7 @@
         <v>1.0395010395010396</v>
       </c>
       <c r="L133" s="11">
-        <v>0</v>
+        <v>0.71225071225071224</v>
       </c>
       <c r="M133" s="11">
         <v>0</v>
@@ -9751,10 +9751,10 @@
         <v>0</v>
       </c>
       <c r="P133" s="11">
-        <v>1.1237758869802537</v>
+        <v>1.0820949357957004</v>
       </c>
       <c r="Q133" s="15">
-        <v>1.1237758869802537</v>
+        <v>1.0820949357957004</v>
       </c>
       <c r="R133" s="12">
         <v>5</v>
@@ -9807,10 +9807,10 @@
         <v>0</v>
       </c>
       <c r="P134" s="11">
-        <v>0.92575448990927611</v>
+        <v>0.88678687555424185</v>
       </c>
       <c r="Q134" s="15">
-        <v>0.78665077473182365</v>
+        <v>0.74989774121710673</v>
       </c>
       <c r="R134" s="12">
         <v>0</v>
@@ -9863,10 +9863,10 @@
         <v>0</v>
       </c>
       <c r="P135" s="11">
-        <v>0.75700227100681305</v>
+        <v>0.7225433526011561</v>
       </c>
       <c r="Q135" s="15">
-        <v>0.75700227100681305</v>
+        <v>0.7225433526011561</v>
       </c>
       <c r="R135" s="12">
         <v>0</v>
@@ -9919,10 +9919,10 @@
         <v>0</v>
       </c>
       <c r="P136" s="11">
-        <v>0.56911597318831419</v>
+        <v>0.51078320090805907</v>
       </c>
       <c r="Q136" s="15">
-        <v>0.56911597318831419</v>
+        <v>0.51078320090805907</v>
       </c>
       <c r="R136" s="12">
         <v>0</v>
@@ -9978,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="Q137" s="15">
-        <v>0.11972360949579257</v>
+        <v>0.11680878402055835</v>
       </c>
       <c r="R137" s="12">
         <v>0</v>
@@ -10034,7 +10034,7 @@
         <v>1.0976948408342482</v>
       </c>
       <c r="Q138" s="15">
-        <v>0.11972360949579257</v>
+        <v>0.11680878402055835</v>
       </c>
       <c r="R138" s="12">
         <v>0</v>
@@ -10075,7 +10075,7 @@
         <v>1.0172939979654121</v>
       </c>
       <c r="L139" s="11">
-        <v>0</v>
+        <v>1.4492753623188406</v>
       </c>
       <c r="M139" s="11">
         <v>0</v>
@@ -10087,10 +10087,10 @@
         <v>0</v>
       </c>
       <c r="P139" s="11">
-        <v>1.179324752341802</v>
+        <v>1.202293606264258</v>
       </c>
       <c r="Q139" s="15">
-        <v>1.179324752341802</v>
+        <v>1.202293606264258</v>
       </c>
       <c r="R139" s="12">
         <v>5</v>
@@ -10143,10 +10143,10 @@
         <v>0</v>
       </c>
       <c r="P140" s="11">
-        <v>1.2</v>
+        <v>1.1312217194570136</v>
       </c>
       <c r="Q140" s="15">
-        <v>1.2</v>
+        <v>1.1312217194570136</v>
       </c>
       <c r="R140" s="12">
         <v>5</v>
@@ -10187,7 +10187,7 @@
         <v>0.90456806874717322</v>
       </c>
       <c r="L141" s="11">
-        <v>0</v>
+        <v>1.2787723785166241</v>
       </c>
       <c r="M141" s="11">
         <v>0</v>
@@ -10199,10 +10199,10 @@
         <v>0</v>
       </c>
       <c r="P141" s="11">
-        <v>1.05517969089442</v>
+        <v>1.0703540847026152</v>
       </c>
       <c r="Q141" s="15">
-        <v>1.05517969089442</v>
+        <v>1.0703540847026152</v>
       </c>
       <c r="R141" s="12">
         <v>5</v>
@@ -10243,7 +10243,7 @@
         <v>1.0070493454179255</v>
       </c>
       <c r="L142" s="11">
-        <v>0</v>
+        <v>1.1013215859030836</v>
       </c>
       <c r="M142" s="11">
         <v>0</v>
@@ -10255,10 +10255,10 @@
         <v>0</v>
       </c>
       <c r="P142" s="11">
-        <v>1.256544502617801</v>
+        <v>1.2430675081277491</v>
       </c>
       <c r="Q142" s="15">
-        <v>1.256544502617801</v>
+        <v>1.2430675081277491</v>
       </c>
       <c r="R142" s="12">
         <v>5</v>
@@ -10299,7 +10299,7 @@
         <v>1.3051044083526682</v>
       </c>
       <c r="L143" s="11">
-        <v>0</v>
+        <v>1.0983646570661461</v>
       </c>
       <c r="M143" s="11">
         <v>0</v>
@@ -10311,10 +10311,10 @@
         <v>0</v>
       </c>
       <c r="P143" s="11">
-        <v>1.4375520014791532</v>
+        <v>1.3835451401033771</v>
       </c>
       <c r="Q143" s="15">
-        <v>1.4375520014791532</v>
+        <v>1.3835451401033771</v>
       </c>
       <c r="R143" s="12">
         <v>5</v>
@@ -10355,7 +10355,7 @@
         <v>0.97323600973236013</v>
       </c>
       <c r="L144" s="11">
-        <v>0</v>
+        <v>1.455796717840127</v>
       </c>
       <c r="M144" s="11">
         <v>0</v>
@@ -10367,10 +10367,10 @@
         <v>0</v>
       </c>
       <c r="P144" s="11">
-        <v>1.304603989563168</v>
+        <v>1.3190938839704727</v>
       </c>
       <c r="Q144" s="15">
-        <v>1.278209668294114</v>
+        <v>1.2666755223257491</v>
       </c>
       <c r="R144" s="12">
         <v>5</v>
@@ -10423,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="P145" s="11">
-        <v>1.6629711751662972</v>
+        <v>1.1017260374586852</v>
       </c>
       <c r="Q145" s="15">
-        <v>1.278209668294114</v>
+        <v>1.2666755223257491</v>
       </c>
       <c r="R145" s="12">
         <v>5</v>
@@ -10467,7 +10467,7 @@
         <v>1.2642225031605563</v>
       </c>
       <c r="L146" s="11">
-        <v>0</v>
+        <v>1.1716461628588166</v>
       </c>
       <c r="M146" s="11">
         <v>0</v>
@@ -10479,10 +10479,10 @@
         <v>0</v>
       </c>
       <c r="P146" s="11">
-        <v>1.3768686073957515</v>
+        <v>1.3600038513383401</v>
       </c>
       <c r="Q146" s="15">
-        <v>1.278209668294114</v>
+        <v>1.2666755223257491</v>
       </c>
       <c r="R146" s="12">
         <v>5</v>
@@ -10523,7 +10523,7 @@
         <v>0.65559440559440563</v>
       </c>
       <c r="L147" s="11">
-        <v>0</v>
+        <v>1.0887316276537833</v>
       </c>
       <c r="M147" s="11">
         <v>0</v>
@@ -10535,10 +10535,10 @@
         <v>0</v>
       </c>
       <c r="P147" s="11">
-        <v>1.006593185364135</v>
+        <v>1.0135446420344605</v>
       </c>
       <c r="Q147" s="15">
-        <v>1.278209668294114</v>
+        <v>1.2666755223257491</v>
       </c>
       <c r="R147" s="12">
         <v>5</v>
@@ -10579,7 +10579,7 @@
         <v>1.0629251700680271</v>
       </c>
       <c r="L148" s="11">
-        <v>0</v>
+        <v>1.3015184381778742</v>
       </c>
       <c r="M148" s="11">
         <v>0</v>
@@ -10591,10 +10591,10 @@
         <v>0</v>
       </c>
       <c r="P148" s="11">
-        <v>1.3125309559187717</v>
+        <v>1.3114025338964215</v>
       </c>
       <c r="Q148" s="15">
-        <v>1.3125309559187717</v>
+        <v>1.3114025338964215</v>
       </c>
       <c r="R148" s="12">
         <v>5</v>
@@ -10635,7 +10635,7 @@
         <v>0.77399380804953566</v>
       </c>
       <c r="L149" s="11">
-        <v>0</v>
+        <v>1.5277171540811874</v>
       </c>
       <c r="M149" s="11">
         <v>0</v>
@@ -10647,10 +10647,10 @@
         <v>0</v>
       </c>
       <c r="P149" s="11">
-        <v>1.0610079575596818</v>
+        <v>1.1009105836692044</v>
       </c>
       <c r="Q149" s="15">
-        <v>1.0810712598568262</v>
+        <v>1.1150608672323015</v>
       </c>
       <c r="R149" s="12">
         <v>5</v>
@@ -10691,7 +10691,7 @@
         <v>0.970873786407767</v>
       </c>
       <c r="L150" s="11">
-        <v>0</v>
+        <v>1.5158077089649198</v>
       </c>
       <c r="M150" s="11">
         <v>0</v>
@@ -10703,10 +10703,10 @@
         <v>0</v>
       </c>
       <c r="P150" s="11">
-        <v>1.0971735499295845</v>
+        <v>1.1266061750197918</v>
       </c>
       <c r="Q150" s="15">
-        <v>1.0810712598568262</v>
+        <v>1.1150608672323015</v>
       </c>
       <c r="R150" s="12">
         <v>5</v>
@@ -10747,7 +10747,7 @@
         <v>1.3629283489096573</v>
       </c>
       <c r="L151" s="11">
-        <v>0</v>
+        <v>1.3763271726307511</v>
       </c>
       <c r="M151" s="11">
         <v>0</v>
@@ -10759,10 +10759,10 @@
         <v>0</v>
       </c>
       <c r="P151" s="11">
-        <v>1.1380304486368924</v>
+        <v>1.1651877744913508</v>
       </c>
       <c r="Q151" s="15">
-        <v>1.1380304486368924</v>
+        <v>1.1651877744913508</v>
       </c>
       <c r="R151" s="12">
         <v>5</v>
@@ -10803,7 +10803,7 @@
         <v>1.0504201680672269</v>
       </c>
       <c r="L152" s="11">
-        <v>0</v>
+        <v>1.4851485148514851</v>
       </c>
       <c r="M152" s="11">
         <v>0</v>
@@ -10815,10 +10815,10 @@
         <v>0</v>
       </c>
       <c r="P152" s="11">
-        <v>1.2897995283018868</v>
+        <v>1.3033337906434352</v>
       </c>
       <c r="Q152" s="15">
-        <v>1.0499865386341201</v>
+        <v>1.0651689745327781</v>
       </c>
       <c r="R152" s="12">
         <v>5</v>
@@ -10859,7 +10859,7 @@
         <v>0.87158628704241725</v>
       </c>
       <c r="L153" s="11">
-        <v>0</v>
+        <v>1.0980966325036603</v>
       </c>
       <c r="M153" s="11">
         <v>0</v>
@@ -10871,10 +10871,10 @@
         <v>0</v>
       </c>
       <c r="P153" s="11">
-        <v>0.97709684983975609</v>
+        <v>0.98877039338936368</v>
       </c>
       <c r="Q153" s="15">
-        <v>1.0499865386341201</v>
+        <v>1.0651689745327781</v>
       </c>
       <c r="R153" s="12">
         <v>5</v>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="11">
-        <v>0</v>
+        <v>0.97911227154046998</v>
       </c>
       <c r="M154" s="11">
         <v>0</v>
@@ -10927,10 +10927,10 @@
         <v>0</v>
       </c>
       <c r="P154" s="11">
-        <v>1.0161126433444623</v>
+        <v>1.0093813086331789</v>
       </c>
       <c r="Q154" s="15">
-        <v>1.0499865386341201</v>
+        <v>1.0651689745327781</v>
       </c>
       <c r="R154" s="12">
         <v>5</v>
@@ -10971,7 +10971,7 @@
         <v>0.53022269353128315</v>
       </c>
       <c r="L155" s="11">
-        <v>0</v>
+        <v>1.321003963011889</v>
       </c>
       <c r="M155" s="11">
         <v>0</v>
@@ -10983,10 +10983,10 @@
         <v>0</v>
       </c>
       <c r="P155" s="11">
-        <v>1.0103926096997691</v>
+        <v>1.0409889394925178</v>
       </c>
       <c r="Q155" s="15">
-        <v>1.0499865386341201</v>
+        <v>1.0651689745327781</v>
       </c>
       <c r="R155" s="12">
         <v>5</v>
@@ -11027,7 +11027,7 @@
         <v>1.0060362173038229</v>
       </c>
       <c r="L156" s="11">
-        <v>0</v>
+        <v>1.5503875968992249</v>
       </c>
       <c r="M156" s="11">
         <v>0</v>
@@ -11039,10 +11039,10 @@
         <v>0</v>
       </c>
       <c r="P156" s="11">
-        <v>1.1381311885883378</v>
+        <v>1.166325015904432</v>
       </c>
       <c r="Q156" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R156" s="12">
         <v>5</v>
@@ -11083,7 +11083,7 @@
         <v>0.86206896551724133</v>
       </c>
       <c r="L157" s="11">
-        <v>0</v>
+        <v>1.3361045130641329</v>
       </c>
       <c r="M157" s="11">
         <v>0</v>
@@ -11095,10 +11095,10 @@
         <v>0</v>
       </c>
       <c r="P157" s="11">
-        <v>1.0687707816540877</v>
+        <v>1.0905918278319033</v>
       </c>
       <c r="Q157" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R157" s="12">
         <v>5</v>
@@ -11139,7 +11139,7 @@
         <v>1.1398176291793314</v>
       </c>
       <c r="L158" s="11">
-        <v>0</v>
+        <v>1.4434180138568129</v>
       </c>
       <c r="M158" s="11">
         <v>0</v>
@@ -11151,10 +11151,10 @@
         <v>0</v>
       </c>
       <c r="P158" s="11">
-        <v>1.3217584282497308</v>
+        <v>1.3341152323706202</v>
       </c>
       <c r="Q158" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R158" s="12">
         <v>5</v>
@@ -11195,7 +11195,7 @@
         <v>1.2686777558500142</v>
       </c>
       <c r="L159" s="11">
-        <v>0</v>
+        <v>1.4836795252225519</v>
       </c>
       <c r="M159" s="11">
         <v>0</v>
@@ -11207,10 +11207,10 @@
         <v>0</v>
       </c>
       <c r="P159" s="11">
-        <v>1.084565562752047</v>
+        <v>1.1149373376989951</v>
       </c>
       <c r="Q159" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R159" s="12">
         <v>5</v>
@@ -11251,7 +11251,7 @@
         <v>1.5105740181268883</v>
       </c>
       <c r="L160" s="11">
-        <v>0</v>
+        <v>0.92764378478664189</v>
       </c>
       <c r="M160" s="11">
         <v>0</v>
@@ -11263,10 +11263,10 @@
         <v>0</v>
       </c>
       <c r="P160" s="11">
-        <v>1.2710207274149394</v>
+        <v>1.2382805589952237</v>
       </c>
       <c r="Q160" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R160" s="12">
         <v>5</v>
@@ -11307,7 +11307,7 @@
         <v>1.2603528988116672</v>
       </c>
       <c r="L161" s="11">
-        <v>0</v>
+        <v>1.6927634363097757</v>
       </c>
       <c r="M161" s="11">
         <v>0</v>
@@ -11319,10 +11319,10 @@
         <v>0</v>
       </c>
       <c r="P161" s="11">
-        <v>1.4111006585136407</v>
+        <v>1.4359242130389378</v>
       </c>
       <c r="Q161" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R161" s="12">
         <v>5</v>
@@ -11363,7 +11363,7 @@
         <v>1.2590494176896443</v>
       </c>
       <c r="L162" s="11">
-        <v>0</v>
+        <v>1.0869565217391304</v>
       </c>
       <c r="M162" s="11">
         <v>0</v>
@@ -11375,10 +11375,10 @@
         <v>0</v>
       </c>
       <c r="P162" s="11">
-        <v>1.3475308478875472</v>
+        <v>1.3326026851321393</v>
       </c>
       <c r="Q162" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R162" s="12">
         <v>5</v>
@@ -11419,7 +11419,7 @@
         <v>1.2648621300278269</v>
       </c>
       <c r="L163" s="11">
-        <v>0</v>
+        <v>1.0940919037199124</v>
       </c>
       <c r="M163" s="11">
         <v>0</v>
@@ -11431,10 +11431,10 @@
         <v>0</v>
       </c>
       <c r="P163" s="11">
-        <v>1.1246569796212156</v>
+        <v>1.1198845949434364</v>
       </c>
       <c r="Q163" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R163" s="12">
         <v>5</v>
@@ -11475,7 +11475,7 @@
         <v>0.95438060698606608</v>
       </c>
       <c r="L164" s="11">
-        <v>0</v>
+        <v>1.4588859416445623</v>
       </c>
       <c r="M164" s="11">
         <v>0</v>
@@ -11487,10 +11487,10 @@
         <v>0</v>
       </c>
       <c r="P164" s="11">
-        <v>1.0317602727435851</v>
+        <v>1.0650618356289034</v>
       </c>
       <c r="Q164" s="15">
-        <v>1.1819789267860485</v>
+        <v>1.1976382434173543</v>
       </c>
       <c r="R164" s="12">
         <v>5</v>
@@ -11531,7 +11531,7 @@
         <v>1.4866204162537167</v>
       </c>
       <c r="L165" s="11">
-        <v>0</v>
+        <v>0.60386473429951693</v>
       </c>
       <c r="M165" s="11">
         <v>0</v>
@@ -11543,10 +11543,10 @@
         <v>0</v>
       </c>
       <c r="P165" s="11">
-        <v>1.0461293215104115</v>
+        <v>1.0124252185918086</v>
       </c>
       <c r="Q165" s="15">
-        <v>1.0461293215104115</v>
+        <v>1.0124252185918086</v>
       </c>
       <c r="R165" s="12">
         <v>5</v>
@@ -11587,7 +11587,7 @@
         <v>0.80515297906602257</v>
       </c>
       <c r="L166" s="11">
-        <v>0</v>
+        <v>1.4326647564469914</v>
       </c>
       <c r="M166" s="11">
         <v>0</v>
@@ -11599,10 +11599,10 @@
         <v>0</v>
       </c>
       <c r="P166" s="11">
-        <v>1.0499790004199916</v>
+        <v>1.098901098901099</v>
       </c>
       <c r="Q166" s="15">
-        <v>1.0499790004199916</v>
+        <v>1.098901098901099</v>
       </c>
       <c r="R166" s="12">
         <v>5</v>
@@ -11655,10 +11655,10 @@
         <v>0</v>
       </c>
       <c r="P167" s="11">
-        <v>0.31433361274098909</v>
+        <v>0.294811320754717</v>
       </c>
       <c r="Q167" s="15">
-        <v>0.78665077473182365</v>
+        <v>0.74989774121710673</v>
       </c>
       <c r="R167" s="12">
         <v>0</v>
@@ -11699,7 +11699,7 @@
         <v>1.8142235123367199</v>
       </c>
       <c r="L168" s="11">
-        <v>0</v>
+        <v>1.8238665971860344</v>
       </c>
       <c r="M168" s="11">
         <v>0</v>
@@ -11711,10 +11711,10 @@
         <v>0</v>
       </c>
       <c r="P168" s="11">
-        <v>1.4917071197411003</v>
+        <v>1.5210878082507491</v>
       </c>
       <c r="Q168" s="15">
-        <v>1.5723659774668812</v>
+        <v>1.6202664271815597</v>
       </c>
       <c r="R168" s="12">
         <v>5</v>
@@ -11755,7 +11755,7 @@
         <v>1.4302741358760429</v>
       </c>
       <c r="L169" s="11">
-        <v>0</v>
+        <v>2.9616724738675959</v>
       </c>
       <c r="M169" s="11">
         <v>0</v>
@@ -11767,10 +11767,10 @@
         <v>0</v>
       </c>
       <c r="P169" s="11">
-        <v>1.9304152637485972</v>
+        <v>2.0481208987870354</v>
       </c>
       <c r="Q169" s="15">
-        <v>1.5723659774668812</v>
+        <v>1.6202664271815597</v>
       </c>
       <c r="R169" s="12">
         <v>5</v>
@@ -11811,7 +11811,7 @@
         <v>0.7706535141800247</v>
       </c>
       <c r="L170" s="11">
-        <v>0</v>
+        <v>1.2658227848101267</v>
       </c>
       <c r="M170" s="11">
         <v>0</v>
@@ -11823,10 +11823,10 @@
         <v>0</v>
       </c>
       <c r="P170" s="11">
-        <v>1.1504740746618003</v>
+        <v>1.1603872792544512</v>
       </c>
       <c r="Q170" s="15">
-        <v>1.2044235191065367</v>
+        <v>1.2052341597796143</v>
       </c>
       <c r="R170" s="12">
         <v>5</v>
@@ -11867,7 +11867,7 @@
         <v>1.4798372179060304</v>
       </c>
       <c r="L171" s="11">
-        <v>0</v>
+        <v>1.1252813203300824</v>
       </c>
       <c r="M171" s="11">
         <v>0</v>
@@ -11879,10 +11879,10 @@
         <v>0</v>
       </c>
       <c r="P171" s="11">
-        <v>1.2708964708182617</v>
+        <v>1.2619888944977284</v>
       </c>
       <c r="Q171" s="15">
-        <v>1.2044235191065367</v>
+        <v>1.2052341597796143</v>
       </c>
       <c r="R171" s="12">
         <v>5</v>
@@ -11923,7 +11923,7 @@
         <v>1.2041744715012042</v>
       </c>
       <c r="L172" s="11">
-        <v>0</v>
+        <v>1.3639906469212784</v>
       </c>
       <c r="M172" s="11">
         <v>0</v>
@@ -11935,10 +11935,10 @@
         <v>0</v>
       </c>
       <c r="P172" s="11">
-        <v>1.3351498637602179</v>
+        <v>1.3386880856760375</v>
       </c>
       <c r="Q172" s="15">
-        <v>1.2433661865049279</v>
+        <v>1.2542603953646898</v>
       </c>
       <c r="R172" s="12">
         <v>5</v>
@@ -11979,7 +11979,7 @@
         <v>1.0718113612004287</v>
       </c>
       <c r="L173" s="11">
-        <v>0</v>
+        <v>1.3227513227513228</v>
       </c>
       <c r="M173" s="11">
         <v>0</v>
@@ -11991,10 +11991,10 @@
         <v>0</v>
       </c>
       <c r="P173" s="11">
-        <v>1.1282051282051282</v>
+        <v>1.1422044545973729</v>
       </c>
       <c r="Q173" s="15">
-        <v>1.2433661865049279</v>
+        <v>1.2542603953646898</v>
       </c>
       <c r="R173" s="12">
         <v>5</v>
@@ -12035,7 +12035,7 @@
         <v>1.1709601873536299</v>
       </c>
       <c r="L174" s="11">
-        <v>0</v>
+        <v>1.4781966001478197</v>
       </c>
       <c r="M174" s="11">
         <v>0</v>
@@ -12047,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="P174" s="11">
-        <v>1.1040686976078511</v>
+        <v>1.1236825790452574</v>
       </c>
       <c r="Q174" s="15">
-        <v>1.1040686976078511</v>
+        <v>1.1236825790452574</v>
       </c>
       <c r="R174" s="12">
         <v>5</v>
@@ -12091,7 +12091,7 @@
         <v>1.4726399007905751</v>
       </c>
       <c r="L175" s="11">
-        <v>0</v>
+        <v>0.64783622700181398</v>
       </c>
       <c r="M175" s="11">
         <v>0</v>
@@ -12103,10 +12103,10 @@
         <v>0</v>
       </c>
       <c r="P175" s="11">
-        <v>1.5638175546186279</v>
+        <v>1.5126512651265127</v>
       </c>
       <c r="Q175" s="15">
-        <v>1.6193994189883114</v>
+        <v>1.5911244186971585</v>
       </c>
       <c r="R175" s="12">
         <v>5</v>
@@ -12147,7 +12147,7 @@
         <v>1.69857936998147</v>
       </c>
       <c r="L176" s="11">
-        <v>0</v>
+        <v>1.5570260801868432</v>
       </c>
       <c r="M176" s="11">
         <v>0</v>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="P176" s="11">
-        <v>1.6738223196325097</v>
+        <v>1.6694852781752743</v>
       </c>
       <c r="Q176" s="15">
-        <v>1.6193994189883114</v>
+        <v>1.5911244186971585</v>
       </c>
       <c r="R176" s="12">
         <v>5</v>
@@ -12203,7 +12203,7 @@
         <v>1.5026296018031555</v>
       </c>
       <c r="L177" s="11">
-        <v>0</v>
+        <v>0.70028011204481788</v>
       </c>
       <c r="M177" s="11">
         <v>0</v>
@@ -12215,10 +12215,10 @@
         <v>0</v>
       </c>
       <c r="P177" s="11">
-        <v>1.7416843111809304</v>
+        <v>1.6491380919783434</v>
       </c>
       <c r="Q177" s="15">
-        <v>1.3721841637473102</v>
+        <v>1.3815529783274751</v>
       </c>
       <c r="R177" s="12">
         <v>5</v>
@@ -12259,7 +12259,7 @@
         <v>1.9637462235649548</v>
       </c>
       <c r="L178" s="11">
-        <v>0</v>
+        <v>1.78051149239236</v>
       </c>
       <c r="M178" s="11">
         <v>0</v>
@@ -12271,10 +12271,10 @@
         <v>0</v>
       </c>
       <c r="P178" s="11">
-        <v>1.5043249341857841</v>
+        <v>1.535899333826795</v>
       </c>
       <c r="Q178" s="15">
-        <v>1.3721841637473102</v>
+        <v>1.3815529783274751</v>
       </c>
       <c r="R178" s="12">
         <v>5</v>
@@ -12315,7 +12315,7 @@
         <v>1.4310246136233544</v>
       </c>
       <c r="L179" s="11">
-        <v>0</v>
+        <v>1.4855687606112054</v>
       </c>
       <c r="M179" s="11">
         <v>0</v>
@@ -12327,10 +12327,10 @@
         <v>0</v>
       </c>
       <c r="P179" s="11">
-        <v>1.3033440083414016</v>
+        <v>1.3180417665183157</v>
       </c>
       <c r="Q179" s="15">
-        <v>1.3721841637473102</v>
+        <v>1.3815529783274751</v>
       </c>
       <c r="R179" s="12">
         <v>5</v>
@@ -12371,7 +12371,7 @@
         <v>1.7605633802816902</v>
       </c>
       <c r="L180" s="11">
-        <v>0</v>
+        <v>1.3220518244315178</v>
       </c>
       <c r="M180" s="11">
         <v>0</v>
@@ -12383,10 +12383,10 @@
         <v>0</v>
       </c>
       <c r="P180" s="11">
-        <v>1.4072237485760235</v>
+        <v>1.3976448197930296</v>
       </c>
       <c r="Q180" s="15">
-        <v>1.3721841637473102</v>
+        <v>1.3815529783274751</v>
       </c>
       <c r="R180" s="12">
         <v>5</v>
@@ -12427,7 +12427,7 @@
         <v>2.0080321285140563</v>
       </c>
       <c r="L181" s="11">
-        <v>0</v>
+        <v>1.4388489208633093</v>
       </c>
       <c r="M181" s="11">
         <v>0</v>
@@ -12439,10 +12439,10 @@
         <v>0</v>
       </c>
       <c r="P181" s="11">
-        <v>0.78325263457704353</v>
+        <v>0.84229622910457436</v>
       </c>
       <c r="Q181" s="15">
-        <v>1.3721841637473102</v>
+        <v>1.3815529783274751</v>
       </c>
       <c r="R181" s="12">
         <v>5</v>
@@ -12483,7 +12483,7 @@
         <v>2.1367521367521367</v>
       </c>
       <c r="L182" s="11">
-        <v>0</v>
+        <v>2.3310023310023311</v>
       </c>
       <c r="M182" s="11">
         <v>0</v>
@@ -12495,10 +12495,10 @@
         <v>0</v>
       </c>
       <c r="P182" s="11">
-        <v>1.3002364066193854</v>
+        <v>1.3951491736424126</v>
       </c>
       <c r="Q182" s="15">
-        <v>1.3721841637473102</v>
+        <v>1.3815529783274751</v>
       </c>
       <c r="R182" s="12">
         <v>5</v>
@@ -12539,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="11">
-        <v>0</v>
+        <v>1.5772870662460567</v>
       </c>
       <c r="M183" s="11">
         <v>0</v>
@@ -12551,10 +12551,10 @@
         <v>0</v>
       </c>
       <c r="P183" s="11">
-        <v>0.76153176675369882</v>
+        <v>0.81416649704864641</v>
       </c>
       <c r="Q183" s="15">
-        <v>1.3721841637473102</v>
+        <v>1.3815529783274751</v>
       </c>
       <c r="R183" s="12">
         <v>5</v>
@@ -12595,7 +12595,7 @@
         <v>1.0351966873706004</v>
       </c>
       <c r="L184" s="11">
-        <v>0</v>
+        <v>1.2525050100200401</v>
       </c>
       <c r="M184" s="11">
         <v>0</v>
@@ -12607,10 +12607,10 @@
         <v>0</v>
       </c>
       <c r="P184" s="11">
-        <v>1.133175048564645</v>
+        <v>1.1543242763274728</v>
       </c>
       <c r="Q184" s="15">
-        <v>1.133175048564645</v>
+        <v>1.1543242763274728</v>
       </c>
       <c r="R184" s="12">
         <v>5</v>
@@ -12707,7 +12707,7 @@
         <v>1.4261266400456361</v>
       </c>
       <c r="L186" s="11">
-        <v>0</v>
+        <v>0.94562647754137119</v>
       </c>
       <c r="M186" s="11">
         <v>0</v>
@@ -12719,10 +12719,10 @@
         <v>0</v>
       </c>
       <c r="P186" s="11">
-        <v>1.0034158838599487</v>
+        <v>0.99862933228901507</v>
       </c>
       <c r="Q186" s="15">
-        <v>0.99709418266765426</v>
+        <v>1.0193275086047127</v>
       </c>
       <c r="R186" s="12">
         <v>5</v>
@@ -12763,7 +12763,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="11">
-        <v>0</v>
+        <v>2.7124773960216997</v>
       </c>
       <c r="M187" s="11">
         <v>0</v>
@@ -12775,10 +12775,10 @@
         <v>0</v>
       </c>
       <c r="P187" s="11">
-        <v>0.98442047594589965</v>
+        <v>1.0625255414793624</v>
       </c>
       <c r="Q187" s="15">
-        <v>0.99709418266765426</v>
+        <v>1.0193275086047127</v>
       </c>
       <c r="R187" s="12">
         <v>5</v>
@@ -12819,7 +12819,7 @@
         <v>0.625</v>
       </c>
       <c r="L188" s="11">
-        <v>0</v>
+        <v>0.86505190311418689</v>
       </c>
       <c r="M188" s="11">
         <v>0</v>
@@ -12831,10 +12831,10 @@
         <v>0</v>
       </c>
       <c r="P188" s="11">
-        <v>1.0230581569213819</v>
+        <v>1.0161836657884833</v>
       </c>
       <c r="Q188" s="15">
-        <v>1.0230581569213819</v>
+        <v>1.0161836657884833</v>
       </c>
       <c r="R188" s="12">
         <v>5</v>
@@ -12887,10 +12887,10 @@
         <v>0</v>
       </c>
       <c r="P189" s="11">
-        <v>0.90057636887608072</v>
+        <v>0.85324232081911267</v>
       </c>
       <c r="Q189" s="15">
-        <v>1.0431484115694643</v>
+        <v>1.0663822980538522</v>
       </c>
       <c r="R189" s="12">
         <v>5</v>
@@ -12931,7 +12931,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="11">
-        <v>0</v>
+        <v>1.3440860215053763</v>
       </c>
       <c r="M190" s="11">
         <v>0</v>
@@ -12943,10 +12943,10 @@
         <v>0</v>
       </c>
       <c r="P190" s="11">
-        <v>1.1964324559495323</v>
+        <v>1.2074864157778225</v>
       </c>
       <c r="Q190" s="15">
-        <v>1.0431484115694643</v>
+        <v>1.0663822980538522</v>
       </c>
       <c r="R190" s="12">
         <v>5</v>
@@ -12987,7 +12987,7 @@
         <v>1.4619883040935673</v>
       </c>
       <c r="L191" s="11">
-        <v>0</v>
+        <v>2.7472527472527473</v>
       </c>
       <c r="M191" s="11">
         <v>0</v>
@@ -12999,10 +12999,10 @@
         <v>0</v>
       </c>
       <c r="P191" s="11">
-        <v>0.94577553593947039</v>
+        <v>1.0435301132975552</v>
       </c>
       <c r="Q191" s="15">
-        <v>1.0431484115694643</v>
+        <v>1.0663822980538522</v>
       </c>
       <c r="R191" s="12">
         <v>5</v>
@@ -13043,7 +13043,7 @@
         <v>2.1246458923512748</v>
       </c>
       <c r="L192" s="11">
-        <v>0</v>
+        <v>2.3734177215189876</v>
       </c>
       <c r="M192" s="11">
         <v>0</v>
@@ -13055,10 +13055,10 @@
         <v>0</v>
       </c>
       <c r="P192" s="11">
-        <v>1.4536025771980827</v>
+        <v>1.5367021656779358</v>
       </c>
       <c r="Q192" s="15">
-        <v>1.4536025771980827</v>
+        <v>1.5367021656779358</v>
       </c>
       <c r="R192" s="12">
         <v>5</v>
@@ -13099,7 +13099,7 @@
         <v>2.7573529411764706</v>
       </c>
       <c r="L193" s="11">
-        <v>0</v>
+        <v>3.3112582781456954</v>
       </c>
       <c r="M193" s="11">
         <v>0</v>
@@ -13111,10 +13111,10 @@
         <v>0</v>
       </c>
       <c r="P193" s="11">
-        <v>1.4465622872702519</v>
+        <v>1.4932802389248383</v>
       </c>
       <c r="Q193" s="15">
-        <v>1.5719246938402487</v>
+        <v>1.565726083964212</v>
       </c>
       <c r="R193" s="12">
         <v>5</v>
@@ -13170,7 +13170,7 @@
         <v>1.6611295681063123</v>
       </c>
       <c r="Q194" s="15">
-        <v>1.5719246938402487</v>
+        <v>1.565726083964212</v>
       </c>
       <c r="R194" s="12">
         <v>5</v>
@@ -13223,10 +13223,10 @@
         <v>0</v>
       </c>
       <c r="P195" s="11">
-        <v>1.2451890423364274</v>
+        <v>1.1451176348115761</v>
       </c>
       <c r="Q195" s="15">
-        <v>1.5719246938402487</v>
+        <v>1.565726083964212</v>
       </c>
       <c r="R195" s="12">
         <v>5</v>
@@ -13267,7 +13267,7 @@
         <v>1.4367816091954022</v>
       </c>
       <c r="L196" s="11">
-        <v>0</v>
+        <v>1.5974440894568691</v>
       </c>
       <c r="M196" s="11">
         <v>0</v>
@@ -13279,10 +13279,10 @@
         <v>0</v>
       </c>
       <c r="P196" s="11">
-        <v>1.1466246237637954</v>
+        <v>1.1837432592397739</v>
       </c>
       <c r="Q196" s="15">
-        <v>1.5719246938402487</v>
+        <v>1.565726083964212</v>
       </c>
       <c r="R196" s="12">
         <v>5</v>
@@ -13323,7 +13323,7 @@
         <v>4.9928673323823114</v>
       </c>
       <c r="L197" s="11">
-        <v>0</v>
+        <v>2.3980815347721824</v>
       </c>
       <c r="M197" s="11">
         <v>0</v>
@@ -13335,10 +13335,10 @@
         <v>0</v>
       </c>
       <c r="P197" s="11">
-        <v>2.5075225677031092</v>
+        <v>2.5013520822065982</v>
       </c>
       <c r="Q197" s="15">
-        <v>1.5719246938402487</v>
+        <v>1.565726083964212</v>
       </c>
       <c r="R197" s="12">
         <v>5</v>
@@ -13391,10 +13391,10 @@
         <v>0</v>
       </c>
       <c r="P198" s="11">
-        <v>0.99840255591054317</v>
+        <v>0.95093191327500948</v>
       </c>
       <c r="Q198" s="15">
-        <v>1.5719246938402487</v>
+        <v>1.565726083964212</v>
       </c>
       <c r="R198" s="12">
         <v>5</v>
@@ -13435,7 +13435,7 @@
         <v>1.2804097311139564</v>
       </c>
       <c r="L199" s="11">
-        <v>0</v>
+        <v>2.2497187851518561</v>
       </c>
       <c r="M199" s="11">
         <v>0</v>
@@ -13447,10 +13447,10 @@
         <v>0</v>
       </c>
       <c r="P199" s="11">
-        <v>1.8978102189781021</v>
+        <v>1.9382349140715855</v>
       </c>
       <c r="Q199" s="15">
-        <v>1.8978102189781021</v>
+        <v>1.9382349140715855</v>
       </c>
       <c r="R199" s="12">
         <v>5</v>
@@ -13491,7 +13491,7 @@
         <v>1.4577259475218658</v>
       </c>
       <c r="L200" s="11">
-        <v>0</v>
+        <v>1.1210762331838564</v>
       </c>
       <c r="M200" s="11">
         <v>0</v>
@@ -13503,10 +13503,10 @@
         <v>0</v>
       </c>
       <c r="P200" s="11">
-        <v>1.152782047340916</v>
+        <v>1.1507479861910241</v>
       </c>
       <c r="Q200" s="15">
-        <v>1.152782047340916</v>
+        <v>1.1507479861910241</v>
       </c>
       <c r="R200" s="12">
         <v>5</v>
@@ -13559,10 +13559,10 @@
         <v>0</v>
       </c>
       <c r="P201" s="11">
-        <v>0.42225767101435674</v>
+        <v>0.38783073343100921</v>
       </c>
       <c r="Q201" s="15">
-        <v>0.42225767101435674</v>
+        <v>0.38783073343100921</v>
       </c>
       <c r="R201" s="12">
         <v>0</v>
@@ -13603,7 +13603,7 @@
         <v>1.3774104683195592</v>
       </c>
       <c r="L202" s="11">
-        <v>0</v>
+        <v>3.0030030030030028</v>
       </c>
       <c r="M202" s="11">
         <v>0</v>
@@ -13615,10 +13615,10 @@
         <v>0</v>
       </c>
       <c r="P202" s="11">
-        <v>1.0080645161290323</v>
+        <v>1.372872048325096</v>
       </c>
       <c r="Q202" s="15">
-        <v>1.1965157461472193</v>
+        <v>1.2014073629108384</v>
       </c>
       <c r="R202" s="12">
         <v>5</v>
@@ -13659,7 +13659,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="11">
-        <v>0</v>
+        <v>2.3255813953488373</v>
       </c>
       <c r="M203" s="11">
         <v>0</v>
@@ -13671,10 +13671,10 @@
         <v>0</v>
       </c>
       <c r="P203" s="11">
-        <v>1.2402551381998583</v>
+        <v>1.3170892327955219</v>
       </c>
       <c r="Q203" s="15">
-        <v>1.1965157461472193</v>
+        <v>1.2014073629108384</v>
       </c>
       <c r="R203" s="12">
         <v>5</v>
@@ -13727,10 +13727,10 @@
         <v>0</v>
       </c>
       <c r="P204" s="11">
-        <v>1.2220954863940037</v>
+        <v>1.1037527593818985</v>
       </c>
       <c r="Q204" s="15">
-        <v>1.1965157461472193</v>
+        <v>1.2014073629108384</v>
       </c>
       <c r="R204" s="12">
         <v>5</v>
@@ -13768,10 +13768,10 @@
         <v>1.3679890560875514</v>
       </c>
       <c r="K205" s="11">
-        <v>1.4771048744460857</v>
+        <v>1.4705882352941178</v>
       </c>
       <c r="L205" s="11">
-        <v>0</v>
+        <v>1.2484394506866416</v>
       </c>
       <c r="M205" s="11">
         <v>0</v>
@@ -13783,10 +13783,10 @@
         <v>0</v>
       </c>
       <c r="P205" s="11">
-        <v>1.1151034568207161</v>
+        <v>1.1267605633802817</v>
       </c>
       <c r="Q205" s="15">
-        <v>1.2655920946055403</v>
+        <v>1.2602160899942549</v>
       </c>
       <c r="R205" s="12">
         <v>5</v>
@@ -13827,7 +13827,7 @@
         <v>2.4958402662229617</v>
       </c>
       <c r="L206" s="11">
-        <v>0</v>
+        <v>0.61728395061728392</v>
       </c>
       <c r="M206" s="11">
         <v>0</v>
@@ -13839,10 +13839,10 @@
         <v>0</v>
       </c>
       <c r="P206" s="11">
-        <v>1.1201792286765881</v>
+        <v>1.0624734381640459</v>
       </c>
       <c r="Q206" s="15">
-        <v>1.2655920946055403</v>
+        <v>1.2602160899942549</v>
       </c>
       <c r="R206" s="12">
         <v>5</v>
@@ -13883,7 +13883,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="11">
-        <v>0</v>
+        <v>1.267427122940431</v>
       </c>
       <c r="M207" s="11">
         <v>0</v>
@@ -13895,10 +13895,10 @@
         <v>0</v>
       </c>
       <c r="P207" s="11">
-        <v>1.4025245441795231</v>
+        <v>1.3877324451845685</v>
       </c>
       <c r="Q207" s="15">
-        <v>1.2655920946055403</v>
+        <v>1.2602160899942549</v>
       </c>
       <c r="R207" s="12">
         <v>5</v>
@@ -13936,10 +13936,10 @@
         <v>0</v>
       </c>
       <c r="K208" s="11">
-        <v>2.3121387283236996</v>
+        <v>2.306805074971165</v>
       </c>
       <c r="L208" s="11">
-        <v>0</v>
+        <v>1.4005602240896358</v>
       </c>
       <c r="M208" s="11">
         <v>0</v>
@@ -13951,10 +13951,10 @@
         <v>0</v>
       </c>
       <c r="P208" s="11">
-        <v>1.2624876495773412</v>
+        <v>1.272264631043257</v>
       </c>
       <c r="Q208" s="15">
-        <v>1.2655920946055403</v>
+        <v>1.2602160899942549</v>
       </c>
       <c r="R208" s="12">
         <v>5</v>
@@ -13992,10 +13992,10 @@
         <v>1.7642907551164433</v>
       </c>
       <c r="K209" s="11">
-        <v>1.348435814455232</v>
+        <v>1.3455328310010763</v>
       </c>
       <c r="L209" s="11">
-        <v>0</v>
+        <v>1.3774104683195592</v>
       </c>
       <c r="M209" s="11">
         <v>0</v>
@@ -14007,10 +14007,10 @@
         <v>0</v>
       </c>
       <c r="P209" s="11">
-        <v>1.3307400962227454</v>
+        <v>1.3337143945889303</v>
       </c>
       <c r="Q209" s="15">
-        <v>1.2655920946055403</v>
+        <v>1.2602160899942549</v>
       </c>
       <c r="R209" s="12">
         <v>5</v>
@@ -14051,7 +14051,7 @@
         <v>1.1627906976744187</v>
       </c>
       <c r="L210" s="11">
-        <v>0</v>
+        <v>1.2738853503184713</v>
       </c>
       <c r="M210" s="11">
         <v>0</v>
@@ -14063,10 +14063,10 @@
         <v>0</v>
       </c>
       <c r="P210" s="11">
-        <v>1.2104283054003724</v>
+        <v>1.2160633484162895</v>
       </c>
       <c r="Q210" s="15">
-        <v>1.2667158387582977</v>
+        <v>1.2859105123184382</v>
       </c>
       <c r="R210" s="12">
         <v>5</v>
@@ -14107,7 +14107,7 @@
         <v>1.2</v>
       </c>
       <c r="L211" s="11">
-        <v>0</v>
+        <v>2.5873221216041395</v>
       </c>
       <c r="M211" s="11">
         <v>0</v>
@@ -14119,10 +14119,10 @@
         <v>0</v>
       </c>
       <c r="P211" s="11">
-        <v>1.5162605876816899</v>
+        <v>1.5963622291021671</v>
       </c>
       <c r="Q211" s="15">
-        <v>1.2667158387582977</v>
+        <v>1.2859105123184382</v>
       </c>
       <c r="R211" s="12">
         <v>5</v>
@@ -14163,7 +14163,7 @@
         <v>1.25</v>
       </c>
       <c r="L212" s="11">
-        <v>0</v>
+        <v>0.72358900144717797</v>
       </c>
       <c r="M212" s="11">
         <v>0</v>
@@ -14175,10 +14175,10 @@
         <v>0</v>
       </c>
       <c r="P212" s="11">
-        <v>0.99818511796733211</v>
+        <v>0.96758587324625056</v>
       </c>
       <c r="Q212" s="15">
-        <v>1.2667158387582977</v>
+        <v>1.2859105123184382</v>
       </c>
       <c r="R212" s="12">
         <v>5</v>
@@ -14219,7 +14219,7 @@
         <v>0.92464170134073043</v>
       </c>
       <c r="L213" s="11">
-        <v>0</v>
+        <v>1.3698630136986301</v>
       </c>
       <c r="M213" s="11">
         <v>0</v>
@@ -14231,10 +14231,10 @@
         <v>0</v>
       </c>
       <c r="P213" s="11">
-        <v>1.1644832605531295</v>
+        <v>1.1767925561029009</v>
       </c>
       <c r="Q213" s="15">
-        <v>0.611653803946966</v>
+        <v>0.62237174095878889</v>
       </c>
       <c r="R213" s="12">
         <v>0</v>
@@ -14287,10 +14287,10 @@
         <v>0</v>
       </c>
       <c r="P214" s="11">
-        <v>0.40042712226374799</v>
+        <v>0.37656903765690375</v>
       </c>
       <c r="Q214" s="15">
-        <v>0.611653803946966</v>
+        <v>0.62237174095878889</v>
       </c>
       <c r="R214" s="12">
         <v>0</v>
@@ -14331,7 +14331,7 @@
         <v>1.1778563015312131</v>
       </c>
       <c r="L215" s="11">
-        <v>0</v>
+        <v>1.2594458438287153</v>
       </c>
       <c r="M215" s="11">
         <v>0</v>
@@ -14343,10 +14343,10 @@
         <v>0</v>
       </c>
       <c r="P215" s="11">
-        <v>0.80813842935919378</v>
+        <v>0.83981612446958986</v>
       </c>
       <c r="Q215" s="15">
-        <v>0.611653803946966</v>
+        <v>0.62237174095878889</v>
       </c>
       <c r="R215" s="12">
         <v>0</v>
@@ -14399,10 +14399,10 @@
         <v>0</v>
       </c>
       <c r="P216" s="11">
-        <v>0.15837820715869497</v>
+        <v>0.14827995255041518</v>
       </c>
       <c r="Q216" s="15">
-        <v>0.611653803946966</v>
+        <v>0.62237174095878889</v>
       </c>
       <c r="R216" s="12">
         <v>0</v>
@@ -14443,7 +14443,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="11">
-        <v>0</v>
+        <v>1.5772870662460567</v>
       </c>
       <c r="M217" s="11">
         <v>0</v>
@@ -14455,10 +14455,10 @@
         <v>0</v>
       </c>
       <c r="P217" s="11">
-        <v>0</v>
+        <v>8.9831117499101693E-2</v>
       </c>
       <c r="Q217" s="15">
-        <v>0.611653803946966</v>
+        <v>0.62237174095878889</v>
       </c>
       <c r="R217" s="12">
         <v>0</v>
@@ -14514,7 +14514,7 @@
         <v>0</v>
       </c>
       <c r="Q218" s="15">
-        <v>0.611653803946966</v>
+        <v>0.62237174095878889</v>
       </c>
       <c r="R218" s="12">
         <v>0</v>
@@ -14555,7 +14555,7 @@
         <v>1.7123287671232876</v>
       </c>
       <c r="L219" s="11">
-        <v>0</v>
+        <v>3.0581039755351682</v>
       </c>
       <c r="M219" s="11">
         <v>0</v>
@@ -14567,10 +14567,10 @@
         <v>0</v>
       </c>
       <c r="P219" s="11">
-        <v>1.1322463768115942</v>
+        <v>1.2650221378874131</v>
       </c>
       <c r="Q219" s="15">
-        <v>1.1322463768115942</v>
+        <v>1.2650221378874131</v>
       </c>
       <c r="R219" s="12">
         <v>5</v>
@@ -14623,10 +14623,10 @@
         <v>0</v>
       </c>
       <c r="P220" s="11">
-        <v>0.43308791684711995</v>
+        <v>0.39872408293460926</v>
       </c>
       <c r="Q220" s="15">
-        <v>0.43308791684711995</v>
+        <v>0.39872408293460926</v>
       </c>
       <c r="R220" s="12">
         <v>0</v>
@@ -14667,7 +14667,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="11">
-        <v>0</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="M221" s="11">
         <v>0</v>
@@ -14679,10 +14679,10 @@
         <v>0</v>
       </c>
       <c r="P221" s="11">
-        <v>0.91279314702991154</v>
+        <v>0.96671730423974589</v>
       </c>
       <c r="Q221" s="15">
-        <v>0.91279314702991154</v>
+        <v>0.96671730423974589</v>
       </c>
       <c r="R221" s="12">
         <v>5</v>
@@ -14723,7 +14723,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="11">
-        <v>0</v>
+        <v>1.3368983957219251</v>
       </c>
       <c r="M222" s="11">
         <v>0</v>
@@ -14735,10 +14735,10 @@
         <v>0</v>
       </c>
       <c r="P222" s="11">
-        <v>1.5757957768673181</v>
+        <v>1.550606146038906</v>
       </c>
       <c r="Q222" s="15">
-        <v>1.5757957768673181</v>
+        <v>1.550606146038906</v>
       </c>
       <c r="R222" s="12">
         <v>5</v>
@@ -14791,10 +14791,10 @@
         <v>0</v>
       </c>
       <c r="P223" s="11">
-        <v>1.0472201066260471</v>
+        <v>1.0038328162073371</v>
       </c>
       <c r="Q223" s="15">
-        <v>1.302990427535671</v>
+        <v>1.3511608233856565</v>
       </c>
       <c r="R223" s="12">
         <v>5</v>
@@ -14835,7 +14835,7 @@
         <v>2.3640661938534278</v>
       </c>
       <c r="L224" s="11">
-        <v>0</v>
+        <v>1.0040160642570282</v>
       </c>
       <c r="M224" s="11">
         <v>0</v>
@@ -14847,10 +14847,10 @@
         <v>0</v>
       </c>
       <c r="P224" s="11">
-        <v>1.4921946740128558</v>
+        <v>1.442109600329625</v>
       </c>
       <c r="Q224" s="15">
-        <v>1.302990427535671</v>
+        <v>1.3511608233856565</v>
       </c>
       <c r="R224" s="12">
         <v>5</v>
@@ -14891,7 +14891,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="11">
-        <v>0</v>
+        <v>4.3103448275862073</v>
       </c>
       <c r="M225" s="11">
         <v>0</v>
@@ -14903,10 +14903,10 @@
         <v>0</v>
       </c>
       <c r="P225" s="11">
-        <v>1.0922992900054616</v>
+        <v>1.222707423580786</v>
       </c>
       <c r="Q225" s="15">
-        <v>1.302990427535671</v>
+        <v>1.3511608233856565</v>
       </c>
       <c r="R225" s="12">
         <v>5</v>
@@ -14947,7 +14947,7 @@
         <v>0.98231827111984282</v>
       </c>
       <c r="L226" s="11">
-        <v>0</v>
+        <v>3.2679738562091503</v>
       </c>
       <c r="M226" s="11">
         <v>0</v>
@@ -14959,10 +14959,10 @@
         <v>0</v>
       </c>
       <c r="P226" s="11">
-        <v>1.1181833820746603</v>
+        <v>1.2256904722993953</v>
       </c>
       <c r="Q226" s="15">
-        <v>1.302990427535671</v>
+        <v>1.3511608233856565</v>
       </c>
       <c r="R226" s="12">
         <v>5</v>
@@ -15003,7 +15003,7 @@
         <v>0.73855243722304287</v>
       </c>
       <c r="L227" s="11">
-        <v>0</v>
+        <v>1.4556040756914119</v>
       </c>
       <c r="M227" s="11">
         <v>0</v>
@@ -15015,10 +15015,10 @@
         <v>0</v>
       </c>
       <c r="P227" s="11">
-        <v>1.3179571663920921</v>
+        <v>1.3276143790849673</v>
       </c>
       <c r="Q227" s="15">
-        <v>1.302990427535671</v>
+        <v>1.3511608233856565</v>
       </c>
       <c r="R227" s="12">
         <v>5</v>
@@ -15059,7 +15059,7 @@
         <v>1.3203063110641668</v>
       </c>
       <c r="L228" s="11">
-        <v>0</v>
+        <v>1.8929150892374256</v>
       </c>
       <c r="M228" s="11">
         <v>0</v>
@@ -15071,10 +15071,10 @@
         <v>0</v>
       </c>
       <c r="P228" s="11">
-        <v>1.6021972991531244</v>
+        <v>1.6529706243506186</v>
       </c>
       <c r="Q228" s="15">
-        <v>1.302990427535671</v>
+        <v>1.3511608233856565</v>
       </c>
       <c r="R228" s="12">
         <v>5</v>
@@ -15115,7 +15115,7 @@
         <v>1.1044176706827309</v>
       </c>
       <c r="L229" s="11">
-        <v>0</v>
+        <v>1.7094017094017093</v>
       </c>
       <c r="M229" s="11">
         <v>0</v>
@@ -15127,10 +15127,10 @@
         <v>0</v>
       </c>
       <c r="P229" s="11">
-        <v>0.97984904092514369</v>
+        <v>1.0345269361347769</v>
       </c>
       <c r="Q229" s="15">
-        <v>0.97984904092514369</v>
+        <v>1.0345269361347769</v>
       </c>
       <c r="R229" s="12">
         <v>5</v>
@@ -15171,7 +15171,7 @@
         <v>1.2456402590931739</v>
       </c>
       <c r="L230" s="11">
-        <v>0</v>
+        <v>0.86355785837651122</v>
       </c>
       <c r="M230" s="11">
         <v>0</v>
@@ -15183,10 +15183,10 @@
         <v>0</v>
       </c>
       <c r="P230" s="11">
-        <v>1.0729613733905579</v>
+        <v>1.0640639906068834</v>
       </c>
       <c r="Q230" s="15">
-        <v>1.0729613733905579</v>
+        <v>1.0640639906068834</v>
       </c>
       <c r="R230" s="12">
         <v>5</v>
@@ -15227,7 +15227,7 @@
         <v>0.85910652920962194</v>
       </c>
       <c r="L231" s="11">
-        <v>0</v>
+        <v>1.1764705882352942</v>
       </c>
       <c r="M231" s="11">
         <v>0</v>
@@ -15239,10 +15239,10 @@
         <v>0</v>
       </c>
       <c r="P231" s="11">
-        <v>1.2439048661558365</v>
+        <v>1.2386457473162675</v>
       </c>
       <c r="Q231" s="15">
-        <v>1.2190547636909228</v>
+        <v>1.2159110647906897</v>
       </c>
       <c r="R231" s="12">
         <v>5</v>
@@ -15298,7 +15298,7 @@
         <v>0.81300813008130079</v>
       </c>
       <c r="Q232" s="15">
-        <v>1.2190547636909228</v>
+        <v>1.2159110647906897</v>
       </c>
       <c r="R232" s="12">
         <v>5</v>
@@ -15339,7 +15339,7 @@
         <v>0</v>
       </c>
       <c r="L233" s="11">
-        <v>0</v>
+        <v>1.3157894736842106</v>
       </c>
       <c r="M233" s="11">
         <v>0</v>
@@ -15351,10 +15351,10 @@
         <v>0</v>
       </c>
       <c r="P233" s="11">
-        <v>1.230827494792653</v>
+        <v>1.2365306482953542</v>
       </c>
       <c r="Q233" s="15">
-        <v>1.0415862973535992</v>
+        <v>1.0449697319112137</v>
       </c>
       <c r="R233" s="12">
         <v>5</v>
@@ -15395,7 +15395,7 @@
         <v>0.78410872974385781</v>
       </c>
       <c r="L234" s="11">
-        <v>0</v>
+        <v>0.93457943925233644</v>
       </c>
       <c r="M234" s="11">
         <v>0</v>
@@ -15407,10 +15407,10 @@
         <v>0</v>
       </c>
       <c r="P234" s="11">
-        <v>0.91145833333333337</v>
+        <v>0.9129640900791236</v>
       </c>
       <c r="Q234" s="15">
-        <v>1.0415862973535992</v>
+        <v>1.0449697319112137</v>
       </c>
       <c r="R234" s="12">
         <v>5</v>
@@ -15451,7 +15451,7 @@
         <v>0</v>
       </c>
       <c r="L235" s="11">
-        <v>0</v>
+        <v>4.2735042735042734</v>
       </c>
       <c r="M235" s="11">
         <v>0</v>
@@ -15463,10 +15463,10 @@
         <v>0</v>
       </c>
       <c r="P235" s="11">
-        <v>0.86956521739130432</v>
+        <v>0.98121670871881128</v>
       </c>
       <c r="Q235" s="15">
-        <v>1.0013865352025881</v>
+        <v>1.0004287551807918</v>
       </c>
       <c r="R235" s="12">
         <v>5</v>
@@ -15519,10 +15519,10 @@
         <v>0</v>
       </c>
       <c r="P236" s="11">
-        <v>1.1509371917132523</v>
+        <v>1.0204081632653061</v>
       </c>
       <c r="Q236" s="15">
-        <v>1.0013865352025881</v>
+        <v>1.0004287551807918</v>
       </c>
       <c r="R236" s="12">
         <v>5</v>
@@ -15563,7 +15563,7 @@
         <v>0.87642418930762489</v>
       </c>
       <c r="L237" s="11">
-        <v>0</v>
+        <v>1.3755158184319121</v>
       </c>
       <c r="M237" s="11">
         <v>0</v>
@@ -15575,10 +15575,10 @@
         <v>0</v>
       </c>
       <c r="P237" s="11">
-        <v>0.85834369265376187</v>
+        <v>0.87968217934165716</v>
       </c>
       <c r="Q237" s="15">
-        <v>0.85834369265376187</v>
+        <v>0.87968217934165716</v>
       </c>
       <c r="R237" s="12">
         <v>4</v>
@@ -15631,10 +15631,10 @@
         <v>0</v>
       </c>
       <c r="P238" s="11">
-        <v>0.95602294455066916</v>
+        <v>0.90198436560432949</v>
       </c>
       <c r="Q238" s="15">
-        <v>0.86374433167782338</v>
+        <v>0.88478175383405422</v>
       </c>
       <c r="R238" s="12">
         <v>4</v>
@@ -15675,7 +15675,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="11">
-        <v>0</v>
+        <v>1.3850415512465375</v>
       </c>
       <c r="M239" s="11">
         <v>0</v>
@@ -15687,10 +15687,10 @@
         <v>0</v>
       </c>
       <c r="P239" s="11">
-        <v>0.81645983017635537</v>
+        <v>0.87642418930762489</v>
       </c>
       <c r="Q239" s="15">
-        <v>0.86374433167782338</v>
+        <v>0.88478175383405422</v>
       </c>
       <c r="R239" s="12">
         <v>4</v>
@@ -15731,7 +15731,7 @@
         <v>0.41528239202657807</v>
       </c>
       <c r="L240" s="11">
-        <v>0</v>
+        <v>1.5511892450879008</v>
       </c>
       <c r="M240" s="11">
         <v>0</v>
@@ -15743,10 +15743,10 @@
         <v>0</v>
       </c>
       <c r="P240" s="11">
-        <v>0.97522917885703142</v>
+        <v>1.0248640941092595</v>
       </c>
       <c r="Q240" s="15">
-        <v>0.97522917885703142</v>
+        <v>1.0248640941092595</v>
       </c>
       <c r="R240" s="12">
         <v>5</v>
@@ -15799,10 +15799,10 @@
         <v>0</v>
       </c>
       <c r="P241" s="11">
-        <v>0.50647565299182407</v>
+        <v>0.46459149133868721</v>
       </c>
       <c r="Q241" s="15">
-        <v>0.50647565299182407</v>
+        <v>0.46459149133868721</v>
       </c>
       <c r="R241" s="12">
         <v>0</v>
@@ -15855,10 +15855,10 @@
         <v>0</v>
       </c>
       <c r="P242" s="11">
-        <v>1.2175324675324675</v>
+        <v>1.1231748408835642</v>
       </c>
       <c r="Q242" s="15">
-        <v>1.2175324675324675</v>
+        <v>1.1231748408835642</v>
       </c>
       <c r="R242" s="12">
         <v>5</v>
@@ -15914,7 +15914,7 @@
         <v>0</v>
       </c>
       <c r="Q243" s="15">
-        <v>0.64824090989451355</v>
+        <v>0.66718558879128209</v>
       </c>
       <c r="R243" s="12">
         <v>0</v>
@@ -15955,7 +15955,7 @@
         <v>1.5384615384615385</v>
       </c>
       <c r="L244" s="11">
-        <v>0</v>
+        <v>1.7182130584192439</v>
       </c>
       <c r="M244" s="11">
         <v>0</v>
@@ -15967,10 +15967,10 @@
         <v>0</v>
       </c>
       <c r="P244" s="11">
-        <v>0.98952270081490101</v>
+        <v>1.0357610117749674</v>
       </c>
       <c r="Q244" s="15">
-        <v>0.64824090989451355</v>
+        <v>0.66718558879128209</v>
       </c>
       <c r="R244" s="12">
         <v>0</v>
@@ -16023,10 +16023,10 @@
         <v>0</v>
       </c>
       <c r="P245" s="11">
-        <v>0.59808612440191389</v>
+        <v>0.57195149851292615</v>
       </c>
       <c r="Q245" s="15">
-        <v>0.64824090989451355</v>
+        <v>0.66718558879128209</v>
       </c>
       <c r="R245" s="12">
         <v>0</v>
@@ -16067,7 +16067,7 @@
         <v>0</v>
       </c>
       <c r="L246" s="11">
-        <v>0</v>
+        <v>2.1276595744680851</v>
       </c>
       <c r="M246" s="11">
         <v>0</v>
@@ -16079,13 +16079,13 @@
         <v>0</v>
       </c>
       <c r="P246" s="11">
-        <v>0.87527352297592997</v>
+        <v>0.99206349206349209</v>
       </c>
       <c r="Q246" s="15">
-        <v>0.87527352297592997</v>
+        <v>0.99206349206349209</v>
       </c>
       <c r="R246" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -16135,10 +16135,10 @@
         <v>0</v>
       </c>
       <c r="P247" s="11">
-        <v>0.48756704046806437</v>
+        <v>0.46721694440118361</v>
       </c>
       <c r="Q247" s="15">
-        <v>0.40101590696430961</v>
+        <v>0.38080731150038083</v>
       </c>
       <c r="R247" s="12">
         <v>0</v>
@@ -16194,7 +16194,7 @@
         <v>0</v>
       </c>
       <c r="Q248" s="15">
-        <v>0.40101590696430961</v>
+        <v>0.38080731150038083</v>
       </c>
       <c r="R248" s="12">
         <v>0</v>
@@ -16247,13 +16247,13 @@
         <v>0</v>
       </c>
       <c r="P249" s="11">
-        <v>0.82792001018978478</v>
+        <v>0.76932181323233517</v>
       </c>
       <c r="Q249" s="15">
-        <v>0.82792001018978478</v>
+        <v>0.76932181323233517</v>
       </c>
       <c r="R249" s="12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.6">
@@ -16291,7 +16291,7 @@
         <v>0.58004640371229699</v>
       </c>
       <c r="L250" s="11">
-        <v>0</v>
+        <v>1.3623978201634876</v>
       </c>
       <c r="M250" s="11">
         <v>0</v>
@@ -16303,10 +16303,10 @@
         <v>0</v>
       </c>
       <c r="P250" s="11">
-        <v>1.0493179433368311</v>
+        <v>1.0768126346015794</v>
       </c>
       <c r="Q250" s="15">
-        <v>1.0102580043518807</v>
+        <v>0.99424756764434341</v>
       </c>
       <c r="R250" s="12">
         <v>5</v>
@@ -16359,10 +16359,10 @@
         <v>0</v>
       </c>
       <c r="P251" s="11">
-        <v>0.95347063310450042</v>
+        <v>0.87366765682334435</v>
       </c>
       <c r="Q251" s="15">
-        <v>1.0102580043518807</v>
+        <v>0.99424756764434341</v>
       </c>
       <c r="R251" s="12">
         <v>5</v>
@@ -16403,7 +16403,7 @@
         <v>1.2605042016806722</v>
       </c>
       <c r="L252" s="11">
-        <v>0</v>
+        <v>1.2886597938144331</v>
       </c>
       <c r="M252" s="11">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="P252" s="11">
-        <v>1.179245283018868</v>
+        <v>1.1951000896325068</v>
       </c>
       <c r="Q252" s="15">
-        <v>1.179245283018868</v>
+        <v>1.1951000896325068</v>
       </c>
       <c r="R252" s="12">
         <v>5</v>
@@ -16459,7 +16459,7 @@
         <v>1.3837638376383763</v>
       </c>
       <c r="L253" s="11">
-        <v>0</v>
+        <v>1.2210012210012211</v>
       </c>
       <c r="M253" s="11">
         <v>0</v>
@@ -16471,10 +16471,10 @@
         <v>0</v>
       </c>
       <c r="P253" s="11">
-        <v>1.066337411606241</v>
+        <v>1.079358552631579</v>
       </c>
       <c r="Q253" s="15">
-        <v>1.066337411606241</v>
+        <v>1.079358552631579</v>
       </c>
       <c r="R253" s="12">
         <v>5</v>
@@ -16515,7 +16515,7 @@
         <v>1.6872890888638921</v>
       </c>
       <c r="L254" s="11">
-        <v>0</v>
+        <v>1.7825311942959001</v>
       </c>
       <c r="M254" s="11">
         <v>0</v>
@@ -16527,10 +16527,10 @@
         <v>0</v>
       </c>
       <c r="P254" s="11">
-        <v>1.2347711557458019</v>
+        <v>1.281085154483798</v>
       </c>
       <c r="Q254" s="15">
-        <v>0.8100314292194537</v>
+        <v>0.86448458832647712</v>
       </c>
       <c r="R254" s="12">
         <v>4</v>
@@ -16583,10 +16583,10 @@
         <v>0</v>
       </c>
       <c r="P255" s="11">
-        <v>0.30974136595942386</v>
+        <v>0.29971527049303159</v>
       </c>
       <c r="Q255" s="15">
-        <v>0.8100314292194537</v>
+        <v>0.86448458832647712</v>
       </c>
       <c r="R255" s="12">
         <v>4</v>
@@ -16627,7 +16627,7 @@
         <v>0.91463414634146345</v>
       </c>
       <c r="L256" s="11">
-        <v>0</v>
+        <v>1.8148820326678765</v>
       </c>
       <c r="M256" s="11">
         <v>0</v>
@@ -16639,10 +16639,10 @@
         <v>0</v>
       </c>
       <c r="P256" s="11">
-        <v>1.1020983953447363</v>
+        <v>1.1652201864352298</v>
       </c>
       <c r="Q256" s="15">
-        <v>0.8100314292194537</v>
+        <v>0.86448458832647712</v>
       </c>
       <c r="R256" s="12">
         <v>4</v>
@@ -16683,7 +16683,7 @@
         <v>0</v>
       </c>
       <c r="L257" s="11">
-        <v>0</v>
+        <v>1.2437810945273631</v>
       </c>
       <c r="M257" s="11">
         <v>0</v>
@@ -16695,10 +16695,10 @@
         <v>0</v>
       </c>
       <c r="P257" s="11">
-        <v>0.42918454935622319</v>
+        <v>0.5132152938157557</v>
       </c>
       <c r="Q257" s="15">
-        <v>0.8100314292194537</v>
+        <v>0.86448458832647712</v>
       </c>
       <c r="R257" s="12">
         <v>4</v>
@@ -16751,10 +16751,10 @@
         <v>0</v>
       </c>
       <c r="P258" s="11">
-        <v>1.0433745714711582</v>
+        <v>0.96299353418627043</v>
       </c>
       <c r="Q258" s="15">
-        <v>1.0433745714711582</v>
+        <v>0.96299353418627043</v>
       </c>
       <c r="R258" s="12">
         <v>5</v>
@@ -16807,10 +16807,10 @@
         <v>0</v>
       </c>
       <c r="P259" s="11">
-        <v>1.0117145899893503</v>
+        <v>0.97807062699474934</v>
       </c>
       <c r="Q259" s="15">
-        <v>0.92416561047739754</v>
+        <v>0.93706845531663052</v>
       </c>
       <c r="R259" s="12">
         <v>5</v>
@@ -16851,7 +16851,7 @@
         <v>0.29958058717795089</v>
       </c>
       <c r="L260" s="11">
-        <v>0</v>
+        <v>1.4749262536873156</v>
       </c>
       <c r="M260" s="11">
         <v>0</v>
@@ -16863,10 +16863,10 @@
         <v>0</v>
       </c>
       <c r="P260" s="11">
-        <v>0.83804734967525663</v>
+        <v>0.89936571049891134</v>
       </c>
       <c r="Q260" s="15">
-        <v>0.92416561047739754</v>
+        <v>0.93706845531663052</v>
       </c>
       <c r="R260" s="12">
         <v>5</v>
@@ -16907,7 +16907,7 @@
         <v>1.0570824524312896</v>
       </c>
       <c r="L261" s="11">
-        <v>0</v>
+        <v>1.1494252873563218</v>
       </c>
       <c r="M261" s="11">
         <v>0</v>
@@ -16919,10 +16919,10 @@
         <v>0</v>
       </c>
       <c r="P261" s="11">
-        <v>1.2601512181461776</v>
+        <v>1.2446799967879225</v>
       </c>
       <c r="Q261" s="15">
-        <v>1.2601512181461776</v>
+        <v>1.2446799967879225</v>
       </c>
       <c r="R261" s="12">
         <v>5</v>
@@ -16975,10 +16975,10 @@
         <v>0</v>
       </c>
       <c r="P262" s="11">
-        <v>1.2734797835084368</v>
+        <v>1.1943863839952225</v>
       </c>
       <c r="Q262" s="15">
-        <v>1.020176830650646</v>
+        <v>1.0281115060364834</v>
       </c>
       <c r="R262" s="12">
         <v>5</v>
@@ -17019,7 +17019,7 @@
         <v>0</v>
       </c>
       <c r="L263" s="11">
-        <v>0</v>
+        <v>1.4164305949008498</v>
       </c>
       <c r="M263" s="11">
         <v>0</v>
@@ -17031,10 +17031,10 @@
         <v>0</v>
       </c>
       <c r="P263" s="11">
-        <v>1.0548523206751055</v>
+        <v>1.1017260374586852</v>
       </c>
       <c r="Q263" s="15">
-        <v>1.020176830650646</v>
+        <v>1.0281115060364834</v>
       </c>
       <c r="R263" s="12">
         <v>5</v>
@@ -17075,7 +17075,7 @@
         <v>1.607717041800643</v>
       </c>
       <c r="L264" s="11">
-        <v>0</v>
+        <v>0.85763293310463118</v>
       </c>
       <c r="M264" s="11">
         <v>0</v>
@@ -17087,10 +17087,10 @@
         <v>0</v>
       </c>
       <c r="P264" s="11">
-        <v>0.90015752756732426</v>
+        <v>0.89673725598399667</v>
       </c>
       <c r="Q264" s="15">
-        <v>1.020176830650646</v>
+        <v>1.0281115060364834</v>
       </c>
       <c r="R264" s="12">
         <v>5</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="L265" s="11">
-        <v>0</v>
+        <v>1.7084282460136675</v>
       </c>
       <c r="M265" s="11">
         <v>0</v>
@@ -17143,10 +17143,10 @@
         <v>0</v>
       </c>
       <c r="P265" s="11">
-        <v>0.99632127529123238</v>
+        <v>1.0807889759524454</v>
       </c>
       <c r="Q265" s="15">
-        <v>1.020176830650646</v>
+        <v>1.0281115060364834</v>
       </c>
       <c r="R265" s="12">
         <v>5</v>
@@ -17255,10 +17255,10 @@
         <v>0</v>
       </c>
       <c r="P267" s="11">
-        <v>0.61156735977634114</v>
+        <v>0.54678956413060464</v>
       </c>
       <c r="Q267" s="15">
-        <v>0.56351100503845131</v>
+        <v>0.51593323216995446</v>
       </c>
       <c r="R267" s="12">
         <v>0</v>
@@ -17311,10 +17311,10 @@
         <v>0</v>
       </c>
       <c r="P268" s="11">
-        <v>0.47370914258645191</v>
+        <v>0.44692737430167595</v>
       </c>
       <c r="Q268" s="15">
-        <v>0.56351100503845131</v>
+        <v>0.51593323216995446</v>
       </c>
       <c r="R268" s="12">
         <v>0</v>
@@ -17367,10 +17367,10 @@
         <v>0</v>
       </c>
       <c r="P269" s="11">
-        <v>0.58377116170461174</v>
+        <v>0.53580996606536879</v>
       </c>
       <c r="Q269" s="15">
-        <v>0.56351100503845131</v>
+        <v>0.51593323216995446</v>
       </c>
       <c r="R269" s="12">
         <v>0</v>
@@ -17411,7 +17411,7 @@
         <v>2.4154589371980677</v>
       </c>
       <c r="L270" s="11">
-        <v>0</v>
+        <v>3.5211267605633805</v>
       </c>
       <c r="M270" s="11">
         <v>0</v>
@@ -17423,10 +17423,10 @@
         <v>0</v>
       </c>
       <c r="P270" s="11">
-        <v>1.2635379061371841</v>
+        <v>1.3736263736263736</v>
       </c>
       <c r="Q270" s="15">
-        <v>1.2635379061371841</v>
+        <v>1.3736263736263736</v>
       </c>
       <c r="R270" s="12">
         <v>5</v>
@@ -17467,7 +17467,7 @@
         <v>0.83857442348008382</v>
       </c>
       <c r="L271" s="11">
-        <v>0</v>
+        <v>1.3979496738117427</v>
       </c>
       <c r="M271" s="11">
         <v>0</v>
@@ -17479,10 +17479,10 @@
         <v>0</v>
       </c>
       <c r="P271" s="11">
-        <v>0.99065949617888482</v>
+        <v>1.0194015126603091</v>
       </c>
       <c r="Q271" s="15">
-        <v>1.1325319811587862</v>
+        <v>1.1429659967615964</v>
       </c>
       <c r="R271" s="12">
         <v>5</v>
@@ -17523,7 +17523,7 @@
         <v>1.5974440894568691</v>
       </c>
       <c r="L272" s="11">
-        <v>0</v>
+        <v>1.3020833333333333</v>
       </c>
       <c r="M272" s="11">
         <v>0</v>
@@ -17535,10 +17535,10 @@
         <v>0</v>
       </c>
       <c r="P272" s="11">
-        <v>1.4373513084853291</v>
+        <v>1.4277818717759765</v>
       </c>
       <c r="Q272" s="15">
-        <v>1.1325319811587862</v>
+        <v>1.1429659967615964</v>
       </c>
       <c r="R272" s="12">
         <v>5</v>
@@ -17579,7 +17579,7 @@
         <v>1.192368839427663</v>
       </c>
       <c r="L273" s="11">
-        <v>0</v>
+        <v>1.4306151645207439</v>
       </c>
       <c r="M273" s="11">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="P273" s="11">
-        <v>1.0125184094256259</v>
+        <v>1.0377929603044194</v>
       </c>
       <c r="Q273" s="15">
-        <v>1.1325319811587862</v>
+        <v>1.1429659967615964</v>
       </c>
       <c r="R273" s="12">
         <v>5</v>
@@ -17635,7 +17635,7 @@
         <v>1</v>
       </c>
       <c r="L274" s="11">
-        <v>0</v>
+        <v>0.82644628099173556</v>
       </c>
       <c r="M274" s="11">
         <v>0</v>
@@ -17647,10 +17647,10 @@
         <v>0</v>
       </c>
       <c r="P274" s="11">
-        <v>1.1945845500398196</v>
+        <v>1.1436413540713632</v>
       </c>
       <c r="Q274" s="15">
-        <v>1.1325319811587862</v>
+        <v>1.1429659967615964</v>
       </c>
       <c r="R274" s="12">
         <v>5</v>
@@ -17703,10 +17703,10 @@
         <v>0</v>
       </c>
       <c r="P275" s="11">
-        <v>0.55834729201563371</v>
+        <v>0.46663555762949138</v>
       </c>
       <c r="Q275" s="15">
-        <v>0.55834729201563371</v>
+        <v>0.46663555762949138</v>
       </c>
       <c r="R275" s="12">
         <v>0</v>
@@ -17747,7 +17747,7 @@
         <v>1.444327731092437</v>
       </c>
       <c r="L276" s="11">
-        <v>0</v>
+        <v>0.95024187975120944</v>
       </c>
       <c r="M276" s="11">
         <v>0</v>
@@ -17759,10 +17759,10 @@
         <v>0</v>
       </c>
       <c r="P276" s="11">
-        <v>1.1742996141586981</v>
+        <v>1.1614803685105373</v>
       </c>
       <c r="Q276" s="15">
-        <v>1.0825409579929468</v>
+        <v>1.092511472674176</v>
       </c>
       <c r="R276" s="12">
         <v>5</v>
@@ -17803,7 +17803,7 @@
         <v>0.83194675540765395</v>
       </c>
       <c r="L277" s="11">
-        <v>0</v>
+        <v>2.2026431718061672</v>
       </c>
       <c r="M277" s="11">
         <v>0</v>
@@ -17815,10 +17815,10 @@
         <v>0</v>
       </c>
       <c r="P277" s="11">
-        <v>1.0490427484920011</v>
+        <v>1.1436138196701577</v>
       </c>
       <c r="Q277" s="15">
-        <v>1.0825409579929468</v>
+        <v>1.092511472674176</v>
       </c>
       <c r="R277" s="12">
         <v>5</v>
@@ -17859,7 +17859,7 @@
         <v>1.5698587127158556</v>
       </c>
       <c r="L278" s="11">
-        <v>0</v>
+        <v>0.99009900990099009</v>
       </c>
       <c r="M278" s="11">
         <v>0</v>
@@ -17871,10 +17871,10 @@
         <v>0</v>
       </c>
       <c r="P278" s="11">
-        <v>0.93759375937593759</v>
+        <v>0.94129131222981455</v>
       </c>
       <c r="Q278" s="15">
-        <v>1.0825409579929468</v>
+        <v>1.092511472674176</v>
       </c>
       <c r="R278" s="12">
         <v>5</v>
@@ -17915,7 +17915,7 @@
         <v>0.91954022988505746</v>
       </c>
       <c r="L279" s="11">
-        <v>0</v>
+        <v>1.2327416173570021</v>
       </c>
       <c r="M279" s="11">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="P279" s="11">
-        <v>1.0768985322271858</v>
+        <v>1.088560885608856</v>
       </c>
       <c r="Q279" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R279" s="12">
         <v>5</v>
@@ -17971,7 +17971,7 @@
         <v>0.73746312684365778</v>
       </c>
       <c r="L280" s="11">
-        <v>0</v>
+        <v>1.6313213703099512</v>
       </c>
       <c r="M280" s="11">
         <v>0</v>
@@ -17983,10 +17983,10 @@
         <v>0</v>
       </c>
       <c r="P280" s="11">
-        <v>1.0316959935805583</v>
+        <v>1.071065174315857</v>
       </c>
       <c r="Q280" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R280" s="12">
         <v>5</v>
@@ -18027,7 +18027,7 @@
         <v>1.3114754098360655</v>
       </c>
       <c r="L281" s="11">
-        <v>0</v>
+        <v>1.2755102040816326</v>
       </c>
       <c r="M281" s="11">
         <v>0</v>
@@ -18039,10 +18039,10 @@
         <v>0</v>
       </c>
       <c r="P281" s="11">
-        <v>1.161140498000258</v>
+        <v>1.1762070124341883</v>
       </c>
       <c r="Q281" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R281" s="12">
         <v>5</v>
@@ -18083,7 +18083,7 @@
         <v>1.0845986984815619</v>
       </c>
       <c r="L282" s="11">
-        <v>0</v>
+        <v>1.2484394506866416</v>
       </c>
       <c r="M282" s="11">
         <v>0</v>
@@ -18095,10 +18095,10 @@
         <v>0</v>
       </c>
       <c r="P282" s="11">
-        <v>1.0560458625631741</v>
+        <v>1.0670081092616304</v>
       </c>
       <c r="Q282" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R282" s="12">
         <v>5</v>
@@ -18139,7 +18139,7 @@
         <v>0.72568940493468792</v>
       </c>
       <c r="L283" s="11">
-        <v>0</v>
+        <v>1.4492753623188406</v>
       </c>
       <c r="M283" s="11">
         <v>0</v>
@@ -18151,10 +18151,10 @@
         <v>0</v>
       </c>
       <c r="P283" s="11">
-        <v>1.1399138731740268</v>
+        <v>1.1721999546245179</v>
       </c>
       <c r="Q283" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R283" s="12">
         <v>5</v>
@@ -18195,7 +18195,7 @@
         <v>1.0162601626016261</v>
       </c>
       <c r="L284" s="11">
-        <v>0</v>
+        <v>2.8735632183908044</v>
       </c>
       <c r="M284" s="11">
         <v>0</v>
@@ -18207,10 +18207,10 @@
         <v>0</v>
       </c>
       <c r="P284" s="11">
-        <v>1.0961907371882709</v>
+        <v>1.1509517485613103</v>
       </c>
       <c r="Q284" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R284" s="12">
         <v>5</v>
@@ -18251,7 +18251,7 @@
         <v>1.5923566878980893</v>
       </c>
       <c r="L285" s="11">
-        <v>0</v>
+        <v>0.81833060556464809</v>
       </c>
       <c r="M285" s="11">
         <v>0</v>
@@ -18263,10 +18263,10 @@
         <v>0</v>
       </c>
       <c r="P285" s="11">
-        <v>1.0939004113065547</v>
+        <v>1.079913606911447</v>
       </c>
       <c r="Q285" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R285" s="12">
         <v>5</v>
@@ -18307,7 +18307,7 @@
         <v>1.3956734124214933</v>
       </c>
       <c r="L286" s="11">
-        <v>0</v>
+        <v>1.8031942297784647</v>
       </c>
       <c r="M286" s="11">
         <v>0</v>
@@ -18319,10 +18319,10 @@
         <v>0</v>
       </c>
       <c r="P286" s="11">
-        <v>1.5095173226317147</v>
+        <v>1.5291045288983576</v>
       </c>
       <c r="Q286" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R286" s="12">
         <v>5</v>
@@ -18363,7 +18363,7 @@
         <v>1.0917030567685591</v>
       </c>
       <c r="L287" s="11">
-        <v>0</v>
+        <v>1.6129032258064515</v>
       </c>
       <c r="M287" s="11">
         <v>0</v>
@@ -18375,10 +18375,10 @@
         <v>0</v>
       </c>
       <c r="P287" s="11">
-        <v>1.0739490641301013</v>
+        <v>1.1060882947003943</v>
       </c>
       <c r="Q287" s="15">
-        <v>1.1694213035149463</v>
+        <v>1.1911913985622837</v>
       </c>
       <c r="R287" s="12">
         <v>5</v>
@@ -18419,7 +18419,7 @@
         <v>1.1415525114155252</v>
       </c>
       <c r="L288" s="11">
-        <v>0</v>
+        <v>1.3054830287206267</v>
       </c>
       <c r="M288" s="11">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         <v>0</v>
       </c>
       <c r="P288" s="11">
-        <v>1.2180267965895251</v>
+        <v>1.2254901960784315</v>
       </c>
       <c r="Q288" s="15">
-        <v>1.2180267965895251</v>
+        <v>1.2254901960784315</v>
       </c>
       <c r="R288" s="12">
         <v>5</v>
@@ -18475,7 +18475,7 @@
         <v>1.179245283018868</v>
       </c>
       <c r="L289" s="11">
-        <v>0</v>
+        <v>0.85910652920962194</v>
       </c>
       <c r="M289" s="11">
         <v>0</v>
@@ -18487,10 +18487,10 @@
         <v>0</v>
       </c>
       <c r="P289" s="11">
-        <v>1.38217000691085</v>
+        <v>1.2321340561853129</v>
       </c>
       <c r="Q289" s="15">
-        <v>1.38217000691085</v>
+        <v>1.2321340561853129</v>
       </c>
       <c r="R289" s="12">
         <v>5</v>
